--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -1752,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347743</v>
+        <v>121346787</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>78598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,47 +1764,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435764</v>
+        <v>436175</v>
       </c>
       <c r="R12" t="n">
-        <v>6737744</v>
+        <v>6737983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121348117</v>
+        <v>121347743</v>
       </c>
       <c r="B13" t="n">
-        <v>100337</v>
+        <v>98071</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,38 +1866,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435853</v>
+        <v>435764</v>
       </c>
       <c r="R13" t="n">
-        <v>6737770</v>
+        <v>6737744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346787</v>
+        <v>121348117</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>100337</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,38 +1977,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436175</v>
+        <v>435853</v>
       </c>
       <c r="R14" t="n">
-        <v>6737983</v>
+        <v>6737770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3198,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347925</v>
+        <v>121347401</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>95365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3210,47 +3210,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435579</v>
+        <v>435964</v>
       </c>
       <c r="R26" t="n">
-        <v>6737662</v>
+        <v>6737892</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347087</v>
+        <v>121347142</v>
       </c>
       <c r="B27" t="n">
-        <v>57501</v>
+        <v>78632</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3325,43 +3316,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436159</v>
+        <v>436148</v>
       </c>
       <c r="R27" t="n">
-        <v>6737985</v>
+        <v>6737987</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347142</v>
+        <v>121347087</v>
       </c>
       <c r="B28" t="n">
-        <v>78632</v>
+        <v>57501</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3436,34 +3418,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436148</v>
+        <v>436159</v>
       </c>
       <c r="R28" t="n">
-        <v>6737987</v>
+        <v>6737985</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347401</v>
+        <v>121347925</v>
       </c>
       <c r="B29" t="n">
-        <v>95365</v>
+        <v>98071</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3534,38 +3525,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435964</v>
+        <v>435579</v>
       </c>
       <c r="R29" t="n">
-        <v>6737892</v>
+        <v>6737662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346682</v>
+        <v>121347759</v>
       </c>
       <c r="B37" t="n">
-        <v>78335</v>
+        <v>78598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4390,34 +4390,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436183</v>
+        <v>435691</v>
       </c>
       <c r="R37" t="n">
-        <v>6738020</v>
+        <v>6737739</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347759</v>
+        <v>121348251</v>
       </c>
       <c r="B38" t="n">
         <v>78598</v>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435691</v>
+        <v>436011</v>
       </c>
       <c r="R38" t="n">
-        <v>6737739</v>
+        <v>6737862</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121348251</v>
+        <v>121346682</v>
       </c>
       <c r="B39" t="n">
-        <v>78598</v>
+        <v>78335</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,34 +4594,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436011</v>
+        <v>436183</v>
       </c>
       <c r="R39" t="n">
-        <v>6737862</v>
+        <v>6738020</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374882</v>
+        <v>121374886</v>
       </c>
       <c r="B47" t="n">
-        <v>90701</v>
+        <v>91965</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>788</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435870</v>
+        <v>435868</v>
       </c>
       <c r="R47" t="n">
-        <v>6737805</v>
+        <v>6737835</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374886</v>
+        <v>121374882</v>
       </c>
       <c r="B48" t="n">
-        <v>91965</v>
+        <v>90701</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,21 +5513,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>788</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435868</v>
+        <v>435870</v>
       </c>
       <c r="R48" t="n">
-        <v>6737835</v>
+        <v>6737805</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347838</v>
+        <v>121346881</v>
       </c>
       <c r="B4" t="n">
-        <v>91127</v>
+        <v>78635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,38 +939,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435602</v>
+        <v>436163</v>
       </c>
       <c r="R4" t="n">
-        <v>6737684</v>
+        <v>6737990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346735</v>
+        <v>121346680</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436168</v>
+        <v>436183</v>
       </c>
       <c r="R5" t="n">
-        <v>6737999</v>
+        <v>6738020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346697</v>
+        <v>121346617</v>
       </c>
       <c r="B6" t="n">
-        <v>74644</v>
+        <v>79219</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436180</v>
+        <v>436197</v>
       </c>
       <c r="R6" t="n">
-        <v>6737996</v>
+        <v>6737992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347850</v>
+        <v>121347275</v>
       </c>
       <c r="B7" t="n">
-        <v>94474</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,38 +1245,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435603</v>
+        <v>436019</v>
       </c>
       <c r="R7" t="n">
-        <v>6737665</v>
+        <v>6737925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347858</v>
+        <v>121347180</v>
       </c>
       <c r="B8" t="n">
-        <v>100337</v>
+        <v>79219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,38 +1356,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435596</v>
+        <v>436132</v>
       </c>
       <c r="R8" t="n">
-        <v>6737662</v>
+        <v>6737977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121348221</v>
+        <v>121347381</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>78635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,47 +1458,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435979</v>
+        <v>435997</v>
       </c>
       <c r="R9" t="n">
-        <v>6737851</v>
+        <v>6737899</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346680</v>
+        <v>121347838</v>
       </c>
       <c r="B10" t="n">
-        <v>78334</v>
+        <v>91137</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,38 +1560,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436183</v>
+        <v>435602</v>
       </c>
       <c r="R10" t="n">
-        <v>6738020</v>
+        <v>6737684</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347170</v>
+        <v>121348117</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>100347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,38 +1662,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436138</v>
+        <v>435853</v>
       </c>
       <c r="R11" t="n">
-        <v>6737980</v>
+        <v>6737770</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346787</v>
+        <v>121347961</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>100347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,38 +1764,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436175</v>
+        <v>435592</v>
       </c>
       <c r="R12" t="n">
-        <v>6737983</v>
+        <v>6737627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347743</v>
+        <v>121347836</v>
       </c>
       <c r="B13" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,47 +1866,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435764</v>
+        <v>435602</v>
       </c>
       <c r="R13" t="n">
-        <v>6737744</v>
+        <v>6737684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121348117</v>
+        <v>121346658</v>
       </c>
       <c r="B14" t="n">
-        <v>100337</v>
+        <v>74647</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,34 +1972,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435853</v>
+        <v>436188</v>
       </c>
       <c r="R14" t="n">
-        <v>6737770</v>
+        <v>6738012</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347180</v>
+        <v>121347170</v>
       </c>
       <c r="B15" t="n">
-        <v>79216</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,21 +2074,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436132</v>
+        <v>436138</v>
       </c>
       <c r="R15" t="n">
-        <v>6737977</v>
+        <v>6737980</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347953</v>
+        <v>121347401</v>
       </c>
       <c r="B16" t="n">
-        <v>100337</v>
+        <v>95375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2176,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435579</v>
+        <v>435964</v>
       </c>
       <c r="R16" t="n">
-        <v>6737637</v>
+        <v>6737892</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347321</v>
+        <v>121347953</v>
       </c>
       <c r="B17" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,38 +2274,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436013</v>
+        <v>435579</v>
       </c>
       <c r="R17" t="n">
-        <v>6737929</v>
+        <v>6737637</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347275</v>
+        <v>121346735</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,47 +2376,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436019</v>
+        <v>436168</v>
       </c>
       <c r="R18" t="n">
-        <v>6737925</v>
+        <v>6737999</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347836</v>
+        <v>121347858</v>
       </c>
       <c r="B19" t="n">
-        <v>90687</v>
+        <v>100347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,25 +2478,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2524,10 +2506,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435602</v>
+        <v>435596</v>
       </c>
       <c r="R19" t="n">
-        <v>6737684</v>
+        <v>6737662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,10 +2568,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347381</v>
+        <v>121347826</v>
       </c>
       <c r="B20" t="n">
-        <v>78632</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2598,38 +2580,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435997</v>
+        <v>435632</v>
       </c>
       <c r="R20" t="n">
-        <v>6737899</v>
+        <v>6737702</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347216</v>
+        <v>121347925</v>
       </c>
       <c r="B21" t="n">
-        <v>79216</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,38 +2691,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436129</v>
+        <v>435579</v>
       </c>
       <c r="R21" t="n">
-        <v>6737975</v>
+        <v>6737662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121348177</v>
+        <v>121347850</v>
       </c>
       <c r="B22" t="n">
-        <v>90652</v>
+        <v>94484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435961</v>
+        <v>435603</v>
       </c>
       <c r="R22" t="n">
-        <v>6737833</v>
+        <v>6737665</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347961</v>
+        <v>121347503</v>
       </c>
       <c r="B23" t="n">
-        <v>100337</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2904,38 +2904,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435592</v>
+        <v>435899</v>
       </c>
       <c r="R23" t="n">
-        <v>6737627</v>
+        <v>6737841</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346569</v>
+        <v>121348302</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,10 +3043,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436212</v>
+        <v>436091</v>
       </c>
       <c r="R24" t="n">
-        <v>6737992</v>
+        <v>6737907</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3096,10 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346658</v>
+        <v>121348177</v>
       </c>
       <c r="B25" t="n">
-        <v>74644</v>
+        <v>90662</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3112,34 +3121,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436188</v>
+        <v>435961</v>
       </c>
       <c r="R25" t="n">
-        <v>6738012</v>
+        <v>6737833</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347401</v>
+        <v>121347949</v>
       </c>
       <c r="B26" t="n">
-        <v>95365</v>
+        <v>98081</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3210,38 +3219,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435964</v>
+        <v>435576</v>
       </c>
       <c r="R26" t="n">
-        <v>6737892</v>
+        <v>6737633</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3300,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347142</v>
+        <v>121347412</v>
       </c>
       <c r="B27" t="n">
-        <v>78632</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3312,38 +3330,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436148</v>
+        <v>435964</v>
       </c>
       <c r="R27" t="n">
-        <v>6737987</v>
+        <v>6737892</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347087</v>
+        <v>121347142</v>
       </c>
       <c r="B28" t="n">
-        <v>57501</v>
+        <v>78635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3418,43 +3445,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436159</v>
+        <v>436148</v>
       </c>
       <c r="R28" t="n">
-        <v>6737985</v>
+        <v>6737987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347925</v>
+        <v>121347321</v>
       </c>
       <c r="B29" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,47 +3543,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435579</v>
+        <v>436013</v>
       </c>
       <c r="R29" t="n">
-        <v>6737662</v>
+        <v>6737929</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347503</v>
+        <v>121348251</v>
       </c>
       <c r="B30" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3636,47 +3645,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435899</v>
+        <v>436011</v>
       </c>
       <c r="R30" t="n">
-        <v>6737841</v>
+        <v>6737862</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346881</v>
+        <v>121346682</v>
       </c>
       <c r="B31" t="n">
-        <v>78632</v>
+        <v>78338</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436163</v>
+        <v>436183</v>
       </c>
       <c r="R31" t="n">
-        <v>6737990</v>
+        <v>6738020</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121348302</v>
+        <v>121347743</v>
       </c>
       <c r="B32" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,38 +3849,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436091</v>
+        <v>435764</v>
       </c>
       <c r="R32" t="n">
-        <v>6737907</v>
+        <v>6737744</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3939,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121347949</v>
+        <v>121346569</v>
       </c>
       <c r="B33" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3951,47 +3960,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435576</v>
+        <v>436212</v>
       </c>
       <c r="R33" t="n">
-        <v>6737633</v>
+        <v>6737992</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347826</v>
+        <v>121347759</v>
       </c>
       <c r="B34" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4062,47 +4062,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435632</v>
+        <v>435691</v>
       </c>
       <c r="R34" t="n">
-        <v>6737702</v>
+        <v>6737739</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347412</v>
+        <v>121346787</v>
       </c>
       <c r="B35" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4173,47 +4164,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435964</v>
+        <v>436175</v>
       </c>
       <c r="R35" t="n">
-        <v>6737892</v>
+        <v>6737983</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346617</v>
+        <v>121347315</v>
       </c>
       <c r="B36" t="n">
-        <v>79216</v>
+        <v>80558</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4288,34 +4270,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436197</v>
+        <v>436015</v>
       </c>
       <c r="R36" t="n">
-        <v>6737992</v>
+        <v>6737908</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347759</v>
+        <v>121347216</v>
       </c>
       <c r="B37" t="n">
-        <v>78598</v>
+        <v>79219</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4390,34 +4372,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435691</v>
+        <v>436129</v>
       </c>
       <c r="R37" t="n">
-        <v>6737739</v>
+        <v>6737975</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121348251</v>
+        <v>121347087</v>
       </c>
       <c r="B38" t="n">
-        <v>78598</v>
+        <v>57504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4492,34 +4474,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436011</v>
+        <v>436159</v>
       </c>
       <c r="R38" t="n">
-        <v>6737862</v>
+        <v>6737985</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346682</v>
+        <v>121348221</v>
       </c>
       <c r="B39" t="n">
-        <v>78335</v>
+        <v>98081</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4590,38 +4581,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436183</v>
+        <v>435979</v>
       </c>
       <c r="R39" t="n">
-        <v>6738020</v>
+        <v>6737851</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121347315</v>
+        <v>121346697</v>
       </c>
       <c r="B40" t="n">
-        <v>80555</v>
+        <v>74647</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4692,38 +4692,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1049</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436015</v>
+        <v>436180</v>
       </c>
       <c r="R40" t="n">
-        <v>6737908</v>
+        <v>6737996</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374883</v>
+        <v>121374886</v>
       </c>
       <c r="B41" t="n">
-        <v>91620</v>
+        <v>91975</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435879</v>
+        <v>435868</v>
       </c>
       <c r="R41" t="n">
-        <v>6737803</v>
+        <v>6737835</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374885</v>
+        <v>121374888</v>
       </c>
       <c r="B42" t="n">
-        <v>98407</v>
+        <v>91380</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219880</v>
+        <v>3298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435878</v>
+        <v>435889</v>
       </c>
       <c r="R42" t="n">
-        <v>6737810</v>
+        <v>6737827</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,10 +4986,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374879</v>
+        <v>121374889</v>
       </c>
       <c r="B43" t="n">
-        <v>91620</v>
+        <v>91985</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5002,21 +5002,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435838</v>
+        <v>435889</v>
       </c>
       <c r="R43" t="n">
-        <v>6737809</v>
+        <v>6737819</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374899</v>
+        <v>121374881</v>
       </c>
       <c r="B44" t="n">
-        <v>91971</v>
+        <v>92004</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,25 +5100,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2058</v>
+        <v>1968</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436217</v>
+        <v>435851</v>
       </c>
       <c r="R44" t="n">
-        <v>6737988</v>
+        <v>6737817</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374892</v>
+        <v>121374885</v>
       </c>
       <c r="B45" t="n">
-        <v>95365</v>
+        <v>98417</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5206,21 +5206,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2869</v>
+        <v>219880</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435973</v>
+        <v>435878</v>
       </c>
       <c r="R45" t="n">
-        <v>6737875</v>
+        <v>6737810</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374891</v>
+        <v>121374883</v>
       </c>
       <c r="B46" t="n">
-        <v>100246</v>
+        <v>91630</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435907</v>
+        <v>435879</v>
       </c>
       <c r="R46" t="n">
-        <v>6737812</v>
+        <v>6737803</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5376,7 +5376,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5395,10 +5394,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374886</v>
+        <v>121374892</v>
       </c>
       <c r="B47" t="n">
-        <v>91965</v>
+        <v>95375</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,25 +5406,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>788</v>
+        <v>2869</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5434,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435868</v>
+        <v>435973</v>
       </c>
       <c r="R47" t="n">
-        <v>6737835</v>
+        <v>6737875</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5500,7 +5499,7 @@
         <v>121374882</v>
       </c>
       <c r="B48" t="n">
-        <v>90701</v>
+        <v>90711</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,10 +5598,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374888</v>
+        <v>121374891</v>
       </c>
       <c r="B49" t="n">
-        <v>91370</v>
+        <v>100256</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,21 +5614,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>222771</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5638,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435889</v>
+        <v>435907</v>
       </c>
       <c r="R49" t="n">
-        <v>6737827</v>
+        <v>6737812</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5683,6 +5682,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374881</v>
+        <v>121374899</v>
       </c>
       <c r="B50" t="n">
-        <v>91994</v>
+        <v>91981</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1968</v>
+        <v>2058</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435851</v>
+        <v>436217</v>
       </c>
       <c r="R50" t="n">
-        <v>6737817</v>
+        <v>6737988</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374889</v>
+        <v>121374879</v>
       </c>
       <c r="B51" t="n">
-        <v>91975</v>
+        <v>91630</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435889</v>
+        <v>435838</v>
       </c>
       <c r="R51" t="n">
-        <v>6737819</v>
+        <v>6737809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -1956,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346658</v>
+        <v>121347401</v>
       </c>
       <c r="B14" t="n">
-        <v>74647</v>
+        <v>95375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1972,34 +1972,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436188</v>
+        <v>435964</v>
       </c>
       <c r="R14" t="n">
-        <v>6738012</v>
+        <v>6737892</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347170</v>
+        <v>121346658</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>74647</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436138</v>
+        <v>436188</v>
       </c>
       <c r="R15" t="n">
-        <v>6737980</v>
+        <v>6738012</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347401</v>
+        <v>121347170</v>
       </c>
       <c r="B16" t="n">
-        <v>95375</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,38 +2172,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435964</v>
+        <v>436138</v>
       </c>
       <c r="R16" t="n">
-        <v>6737892</v>
+        <v>6737980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347142</v>
+        <v>121348251</v>
       </c>
       <c r="B28" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,34 +3445,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436148</v>
+        <v>436011</v>
       </c>
       <c r="R28" t="n">
-        <v>6737987</v>
+        <v>6737862</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347321</v>
+        <v>121347142</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>78635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436013</v>
+        <v>436148</v>
       </c>
       <c r="R29" t="n">
-        <v>6737929</v>
+        <v>6737987</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121348251</v>
+        <v>121347321</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3649,34 +3649,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436011</v>
+        <v>436013</v>
       </c>
       <c r="R30" t="n">
-        <v>6737862</v>
+        <v>6737929</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121346569</v>
+        <v>121347315</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>80558</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3964,34 +3964,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436212</v>
+        <v>436015</v>
       </c>
       <c r="R33" t="n">
-        <v>6737992</v>
+        <v>6737908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347759</v>
+        <v>121346569</v>
       </c>
       <c r="B34" t="n">
         <v>78601</v>
@@ -4086,14 +4086,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435691</v>
+        <v>436212</v>
       </c>
       <c r="R34" t="n">
-        <v>6737739</v>
+        <v>6737992</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346787</v>
+        <v>121347759</v>
       </c>
       <c r="B35" t="n">
         <v>78601</v>
@@ -4188,14 +4188,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436175</v>
+        <v>435691</v>
       </c>
       <c r="R35" t="n">
-        <v>6737983</v>
+        <v>6737739</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121347315</v>
+        <v>121346787</v>
       </c>
       <c r="B36" t="n">
-        <v>80558</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,34 +4270,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436015</v>
+        <v>436175</v>
       </c>
       <c r="R36" t="n">
-        <v>6737908</v>
+        <v>6737983</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347216</v>
+        <v>121348221</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>98081</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,38 +4368,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436129</v>
+        <v>435979</v>
       </c>
       <c r="R37" t="n">
-        <v>6737975</v>
+        <v>6737851</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,10 +4467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347087</v>
+        <v>121347216</v>
       </c>
       <c r="B38" t="n">
-        <v>57504</v>
+        <v>79219</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,43 +4483,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436159</v>
+        <v>436129</v>
       </c>
       <c r="R38" t="n">
-        <v>6737985</v>
+        <v>6737975</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121348221</v>
+        <v>121347087</v>
       </c>
       <c r="B39" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4581,47 +4581,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435979</v>
+        <v>436159</v>
       </c>
       <c r="R39" t="n">
-        <v>6737851</v>
+        <v>6737985</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346680</v>
+        <v>121346617</v>
       </c>
       <c r="B5" t="n">
-        <v>78337</v>
+        <v>79219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436183</v>
+        <v>436197</v>
       </c>
       <c r="R5" t="n">
-        <v>6738020</v>
+        <v>6737992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346617</v>
+        <v>121346680</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>78337</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436197</v>
+        <v>436183</v>
       </c>
       <c r="R6" t="n">
-        <v>6737992</v>
+        <v>6738020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347850</v>
+        <v>121347503</v>
       </c>
       <c r="B22" t="n">
-        <v>94484</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2802,38 +2802,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435603</v>
+        <v>435899</v>
       </c>
       <c r="R22" t="n">
-        <v>6737665</v>
+        <v>6737841</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347503</v>
+        <v>121347850</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>94484</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2904,47 +2913,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435899</v>
+        <v>435603</v>
       </c>
       <c r="R23" t="n">
-        <v>6737841</v>
+        <v>6737665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3429,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121348251</v>
+        <v>121347142</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,34 +3445,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436011</v>
+        <v>436148</v>
       </c>
       <c r="R28" t="n">
-        <v>6737862</v>
+        <v>6737987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347142</v>
+        <v>121347321</v>
       </c>
       <c r="B29" t="n">
-        <v>78635</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,21 +3547,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436148</v>
+        <v>436013</v>
       </c>
       <c r="R29" t="n">
-        <v>6737987</v>
+        <v>6737929</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347321</v>
+        <v>121348251</v>
       </c>
       <c r="B30" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3649,34 +3649,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436013</v>
+        <v>436011</v>
       </c>
       <c r="R30" t="n">
-        <v>6737929</v>
+        <v>6737862</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121347315</v>
+        <v>121346569</v>
       </c>
       <c r="B33" t="n">
-        <v>80558</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3964,34 +3964,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436015</v>
+        <v>436212</v>
       </c>
       <c r="R33" t="n">
-        <v>6737908</v>
+        <v>6737992</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121346569</v>
+        <v>121347759</v>
       </c>
       <c r="B34" t="n">
         <v>78601</v>
@@ -4086,14 +4086,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436212</v>
+        <v>435691</v>
       </c>
       <c r="R34" t="n">
-        <v>6737992</v>
+        <v>6737739</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4152,7 +4152,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347759</v>
+        <v>121346787</v>
       </c>
       <c r="B35" t="n">
         <v>78601</v>
@@ -4188,14 +4188,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435691</v>
+        <v>436175</v>
       </c>
       <c r="R35" t="n">
-        <v>6737739</v>
+        <v>6737983</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346787</v>
+        <v>121347315</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>80558</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,34 +4270,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436175</v>
+        <v>436015</v>
       </c>
       <c r="R36" t="n">
-        <v>6737983</v>
+        <v>6737908</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121348221</v>
+        <v>121347216</v>
       </c>
       <c r="B37" t="n">
-        <v>98081</v>
+        <v>79219</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,47 +4368,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435979</v>
+        <v>436129</v>
       </c>
       <c r="R37" t="n">
-        <v>6737851</v>
+        <v>6737975</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347216</v>
+        <v>121347087</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
+        <v>57504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4483,34 +4474,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436129</v>
+        <v>436159</v>
       </c>
       <c r="R38" t="n">
-        <v>6737975</v>
+        <v>6737985</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121347087</v>
+        <v>121348221</v>
       </c>
       <c r="B39" t="n">
-        <v>57504</v>
+        <v>98081</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4581,47 +4581,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436159</v>
+        <v>435979</v>
       </c>
       <c r="R39" t="n">
-        <v>6737985</v>
+        <v>6737851</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346881</v>
+        <v>121346569</v>
       </c>
       <c r="B4" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436163</v>
+        <v>436212</v>
       </c>
       <c r="R4" t="n">
-        <v>6737990</v>
+        <v>6737992</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346617</v>
+        <v>121347925</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1041,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436197</v>
+        <v>435579</v>
       </c>
       <c r="R5" t="n">
-        <v>6737992</v>
+        <v>6737662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346680</v>
+        <v>121348177</v>
       </c>
       <c r="B6" t="n">
-        <v>78337</v>
+        <v>90662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,38 +1152,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436183</v>
+        <v>435961</v>
       </c>
       <c r="R6" t="n">
-        <v>6738020</v>
+        <v>6737833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347275</v>
+        <v>121346682</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>78338</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,47 +1254,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436019</v>
+        <v>436183</v>
       </c>
       <c r="R7" t="n">
-        <v>6737925</v>
+        <v>6738020</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347180</v>
+        <v>121347381</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>78635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,34 +1360,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436132</v>
+        <v>435997</v>
       </c>
       <c r="R8" t="n">
-        <v>6737977</v>
+        <v>6737899</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347381</v>
+        <v>121347142</v>
       </c>
       <c r="B9" t="n">
         <v>78635</v>
@@ -1482,14 +1482,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435997</v>
+        <v>436148</v>
       </c>
       <c r="R9" t="n">
-        <v>6737899</v>
+        <v>6737987</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347838</v>
+        <v>121347953</v>
       </c>
       <c r="B10" t="n">
-        <v>91137</v>
+        <v>100347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435602</v>
+        <v>435579</v>
       </c>
       <c r="R10" t="n">
-        <v>6737684</v>
+        <v>6737637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121348117</v>
+        <v>121347321</v>
       </c>
       <c r="B11" t="n">
-        <v>100347</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,38 +1662,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435853</v>
+        <v>436013</v>
       </c>
       <c r="R11" t="n">
-        <v>6737770</v>
+        <v>6737929</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347961</v>
+        <v>121347087</v>
       </c>
       <c r="B12" t="n">
-        <v>100347</v>
+        <v>57504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,38 +1764,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435592</v>
+        <v>436159</v>
       </c>
       <c r="R12" t="n">
-        <v>6737627</v>
+        <v>6737985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347836</v>
+        <v>121346617</v>
       </c>
       <c r="B13" t="n">
-        <v>90697</v>
+        <v>79219</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1870,34 +1879,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435602</v>
+        <v>436197</v>
       </c>
       <c r="R13" t="n">
-        <v>6737684</v>
+        <v>6737992</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347401</v>
+        <v>121347315</v>
       </c>
       <c r="B14" t="n">
-        <v>95375</v>
+        <v>80558</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,25 +1977,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>1049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1996,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435964</v>
+        <v>436015</v>
       </c>
       <c r="R14" t="n">
-        <v>6737892</v>
+        <v>6737908</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346658</v>
+        <v>121347858</v>
       </c>
       <c r="B15" t="n">
-        <v>74647</v>
+        <v>100347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2074,34 +2083,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436188</v>
+        <v>435596</v>
       </c>
       <c r="R15" t="n">
-        <v>6738012</v>
+        <v>6737662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347170</v>
+        <v>121347961</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>100347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,38 +2181,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436138</v>
+        <v>435592</v>
       </c>
       <c r="R16" t="n">
-        <v>6737980</v>
+        <v>6737627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347953</v>
+        <v>121346881</v>
       </c>
       <c r="B17" t="n">
-        <v>100347</v>
+        <v>78635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,38 +2283,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435579</v>
+        <v>436163</v>
       </c>
       <c r="R17" t="n">
-        <v>6737637</v>
+        <v>6737990</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346735</v>
+        <v>121347838</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>91137</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2376,38 +2385,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436168</v>
+        <v>435602</v>
       </c>
       <c r="R18" t="n">
-        <v>6737999</v>
+        <v>6737684</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347858</v>
+        <v>121347401</v>
       </c>
       <c r="B19" t="n">
-        <v>100347</v>
+        <v>95375</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2506,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435596</v>
+        <v>435964</v>
       </c>
       <c r="R19" t="n">
-        <v>6737662</v>
+        <v>6737892</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347826</v>
+        <v>121348302</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,47 +2589,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435632</v>
+        <v>436091</v>
       </c>
       <c r="R20" t="n">
-        <v>6737702</v>
+        <v>6737907</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347925</v>
+        <v>121347503</v>
       </c>
       <c r="B21" t="n">
         <v>98081</v>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435579</v>
+        <v>435899</v>
       </c>
       <c r="R21" t="n">
-        <v>6737662</v>
+        <v>6737841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347503</v>
+        <v>121348221</v>
       </c>
       <c r="B22" t="n">
         <v>98081</v>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435899</v>
+        <v>435979</v>
       </c>
       <c r="R22" t="n">
-        <v>6737841</v>
+        <v>6737851</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347850</v>
+        <v>121347949</v>
       </c>
       <c r="B23" t="n">
-        <v>94484</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,38 +2913,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435603</v>
+        <v>435576</v>
       </c>
       <c r="R23" t="n">
-        <v>6737665</v>
+        <v>6737633</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121348302</v>
+        <v>121348117</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>100347</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,38 +3024,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436091</v>
+        <v>435853</v>
       </c>
       <c r="R24" t="n">
-        <v>6737907</v>
+        <v>6737770</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,10 +3114,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121348177</v>
+        <v>121347836</v>
       </c>
       <c r="B25" t="n">
-        <v>90662</v>
+        <v>90697</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,25 +3126,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3145,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435961</v>
+        <v>435602</v>
       </c>
       <c r="R25" t="n">
-        <v>6737833</v>
+        <v>6737684</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347949</v>
+        <v>121347180</v>
       </c>
       <c r="B26" t="n">
-        <v>98081</v>
+        <v>79219</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,47 +3228,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435576</v>
+        <v>436132</v>
       </c>
       <c r="R26" t="n">
-        <v>6737633</v>
+        <v>6737977</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347412</v>
+        <v>121346680</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>78337</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3330,47 +3330,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435964</v>
+        <v>436183</v>
       </c>
       <c r="R27" t="n">
-        <v>6737892</v>
+        <v>6738020</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3420,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347142</v>
+        <v>121347170</v>
       </c>
       <c r="B28" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3445,21 +3436,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3469,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436148</v>
+        <v>436138</v>
       </c>
       <c r="R28" t="n">
-        <v>6737987</v>
+        <v>6737980</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3522,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347321</v>
+        <v>121347216</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>79219</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3547,21 +3538,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3571,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436013</v>
+        <v>436129</v>
       </c>
       <c r="R29" t="n">
-        <v>6737929</v>
+        <v>6737975</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,10 +3624,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121348251</v>
+        <v>121347743</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3645,38 +3636,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436011</v>
+        <v>435764</v>
       </c>
       <c r="R30" t="n">
-        <v>6737862</v>
+        <v>6737744</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346682</v>
+        <v>121347759</v>
       </c>
       <c r="B31" t="n">
-        <v>78338</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3751,34 +3751,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436183</v>
+        <v>435691</v>
       </c>
       <c r="R31" t="n">
-        <v>6738020</v>
+        <v>6737739</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,7 +3837,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347743</v>
+        <v>121347275</v>
       </c>
       <c r="B32" t="n">
         <v>98081</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3882,14 +3882,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435764</v>
+        <v>436019</v>
       </c>
       <c r="R32" t="n">
-        <v>6737744</v>
+        <v>6737925</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121346569</v>
+        <v>121347412</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,38 +3960,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436212</v>
+        <v>435964</v>
       </c>
       <c r="R33" t="n">
-        <v>6737992</v>
+        <v>6737892</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,7 +4059,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347759</v>
+        <v>121346735</v>
       </c>
       <c r="B34" t="n">
         <v>78601</v>
@@ -4086,14 +4095,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435691</v>
+        <v>436168</v>
       </c>
       <c r="R34" t="n">
-        <v>6737739</v>
+        <v>6737999</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4152,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346787</v>
+        <v>121346658</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
+        <v>74647</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,25 +4173,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4192,10 +4201,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436175</v>
+        <v>436188</v>
       </c>
       <c r="R35" t="n">
-        <v>6737983</v>
+        <v>6738012</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,10 +4263,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121347315</v>
+        <v>121348251</v>
       </c>
       <c r="B36" t="n">
-        <v>80558</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,21 +4279,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,10 +4303,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436015</v>
+        <v>436011</v>
       </c>
       <c r="R36" t="n">
-        <v>6737908</v>
+        <v>6737862</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,10 +4365,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347216</v>
+        <v>121347850</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>94484</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,38 +4377,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>2809</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436129</v>
+        <v>435603</v>
       </c>
       <c r="R37" t="n">
-        <v>6737975</v>
+        <v>6737665</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,10 +4467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347087</v>
+        <v>121346787</v>
       </c>
       <c r="B38" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,43 +4483,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436159</v>
+        <v>436175</v>
       </c>
       <c r="R38" t="n">
-        <v>6737985</v>
+        <v>6737983</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121348221</v>
+        <v>121346697</v>
       </c>
       <c r="B39" t="n">
-        <v>98081</v>
+        <v>74647</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4581,47 +4581,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435979</v>
+        <v>436180</v>
       </c>
       <c r="R39" t="n">
-        <v>6737851</v>
+        <v>6737996</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121346697</v>
+        <v>121347826</v>
       </c>
       <c r="B40" t="n">
-        <v>74647</v>
+        <v>98081</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4692,38 +4683,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436180</v>
+        <v>435632</v>
       </c>
       <c r="R40" t="n">
-        <v>6737996</v>
+        <v>6737702</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374886</v>
+        <v>121374891</v>
       </c>
       <c r="B41" t="n">
-        <v>91975</v>
+        <v>100256</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>788</v>
+        <v>222771</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435868</v>
+        <v>435907</v>
       </c>
       <c r="R41" t="n">
-        <v>6737835</v>
+        <v>6737812</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4866,6 +4866,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4884,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374888</v>
+        <v>121374885</v>
       </c>
       <c r="B42" t="n">
-        <v>91380</v>
+        <v>98417</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4900,21 +4901,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>219880</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4925,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435889</v>
+        <v>435878</v>
       </c>
       <c r="R42" t="n">
-        <v>6737827</v>
+        <v>6737810</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374889</v>
+        <v>121374882</v>
       </c>
       <c r="B43" t="n">
-        <v>91985</v>
+        <v>90711</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,25 +4999,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435889</v>
+        <v>435870</v>
       </c>
       <c r="R43" t="n">
-        <v>6737819</v>
+        <v>6737805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5088,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374881</v>
+        <v>121374889</v>
       </c>
       <c r="B44" t="n">
-        <v>92004</v>
+        <v>91985</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,25 +5101,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5128,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435851</v>
+        <v>435889</v>
       </c>
       <c r="R44" t="n">
-        <v>6737817</v>
+        <v>6737819</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5190,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374885</v>
+        <v>121374886</v>
       </c>
       <c r="B45" t="n">
-        <v>98417</v>
+        <v>91975</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,25 +5203,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219880</v>
+        <v>788</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5230,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435878</v>
+        <v>435868</v>
       </c>
       <c r="R45" t="n">
-        <v>6737810</v>
+        <v>6737835</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5292,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374883</v>
+        <v>121374881</v>
       </c>
       <c r="B46" t="n">
-        <v>91630</v>
+        <v>92004</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>1968</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5332,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435879</v>
+        <v>435851</v>
       </c>
       <c r="R46" t="n">
-        <v>6737803</v>
+        <v>6737817</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5394,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374892</v>
+        <v>121374883</v>
       </c>
       <c r="B47" t="n">
-        <v>95375</v>
+        <v>91630</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5410,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2869</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5434,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435973</v>
+        <v>435879</v>
       </c>
       <c r="R47" t="n">
-        <v>6737875</v>
+        <v>6737803</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5496,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374882</v>
+        <v>121374892</v>
       </c>
       <c r="B48" t="n">
-        <v>90711</v>
+        <v>95375</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5536,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435870</v>
+        <v>435973</v>
       </c>
       <c r="R48" t="n">
-        <v>6737805</v>
+        <v>6737875</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5598,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374891</v>
+        <v>121374888</v>
       </c>
       <c r="B49" t="n">
-        <v>100256</v>
+        <v>91380</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5614,21 +5615,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222771</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5638,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435907</v>
+        <v>435889</v>
       </c>
       <c r="R49" t="n">
-        <v>6737812</v>
+        <v>6737827</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5682,7 +5683,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121348177</v>
+        <v>121346682</v>
       </c>
       <c r="B6" t="n">
-        <v>90662</v>
+        <v>78338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1152,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435961</v>
+        <v>436183</v>
       </c>
       <c r="R6" t="n">
-        <v>6737833</v>
+        <v>6738020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346682</v>
+        <v>121348177</v>
       </c>
       <c r="B7" t="n">
-        <v>78338</v>
+        <v>90662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1254,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436183</v>
+        <v>435961</v>
       </c>
       <c r="R7" t="n">
-        <v>6738020</v>
+        <v>6737833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347953</v>
+        <v>121346617</v>
       </c>
       <c r="B10" t="n">
-        <v>100347</v>
+        <v>79219</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,38 +1560,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435579</v>
+        <v>436197</v>
       </c>
       <c r="R10" t="n">
-        <v>6737637</v>
+        <v>6737992</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347321</v>
+        <v>121347953</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>100347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,38 +1662,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436013</v>
+        <v>435579</v>
       </c>
       <c r="R11" t="n">
-        <v>6737929</v>
+        <v>6737637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347087</v>
+        <v>121347321</v>
       </c>
       <c r="B12" t="n">
-        <v>57504</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,43 +1768,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436159</v>
+        <v>436013</v>
       </c>
       <c r="R12" t="n">
-        <v>6737985</v>
+        <v>6737929</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346617</v>
+        <v>121347087</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>57504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,34 +1870,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436197</v>
+        <v>436159</v>
       </c>
       <c r="R13" t="n">
-        <v>6737992</v>
+        <v>6737985</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347315</v>
+        <v>121347858</v>
       </c>
       <c r="B14" t="n">
-        <v>80558</v>
+        <v>100347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,25 +1977,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436015</v>
+        <v>435596</v>
       </c>
       <c r="R14" t="n">
-        <v>6737908</v>
+        <v>6737662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347858</v>
+        <v>121347315</v>
       </c>
       <c r="B15" t="n">
-        <v>100347</v>
+        <v>80558</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,25 +2079,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435596</v>
+        <v>436015</v>
       </c>
       <c r="R15" t="n">
-        <v>6737662</v>
+        <v>6737908</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347961</v>
+        <v>121346881</v>
       </c>
       <c r="B16" t="n">
-        <v>100347</v>
+        <v>78635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,38 +2181,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435592</v>
+        <v>436163</v>
       </c>
       <c r="R16" t="n">
-        <v>6737627</v>
+        <v>6737990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346881</v>
+        <v>121347961</v>
       </c>
       <c r="B17" t="n">
-        <v>78635</v>
+        <v>100347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,38 +2283,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436163</v>
+        <v>435592</v>
       </c>
       <c r="R17" t="n">
-        <v>6737990</v>
+        <v>6737627</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121348302</v>
+        <v>121347503</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,38 +2589,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436091</v>
+        <v>435899</v>
       </c>
       <c r="R20" t="n">
-        <v>6737907</v>
+        <v>6737841</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347503</v>
+        <v>121348302</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,47 +2700,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435899</v>
+        <v>436091</v>
       </c>
       <c r="R21" t="n">
-        <v>6737841</v>
+        <v>6737907</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374883</v>
+        <v>121374892</v>
       </c>
       <c r="B47" t="n">
-        <v>91630</v>
+        <v>95375</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>2869</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435879</v>
+        <v>435973</v>
       </c>
       <c r="R47" t="n">
-        <v>6737803</v>
+        <v>6737875</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374892</v>
+        <v>121374883</v>
       </c>
       <c r="B48" t="n">
-        <v>95375</v>
+        <v>91630</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,21 +5513,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435973</v>
+        <v>435879</v>
       </c>
       <c r="R48" t="n">
-        <v>6737875</v>
+        <v>6737803</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346569</v>
+        <v>121346881</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>78638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436212</v>
+        <v>436163</v>
       </c>
       <c r="R4" t="n">
-        <v>6737992</v>
+        <v>6737990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347925</v>
+        <v>121347142</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>78638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,47 +1041,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435579</v>
+        <v>436148</v>
       </c>
       <c r="R5" t="n">
-        <v>6737662</v>
+        <v>6737987</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346682</v>
+        <v>121347401</v>
       </c>
       <c r="B6" t="n">
-        <v>78338</v>
+        <v>95388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1143,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436183</v>
+        <v>435964</v>
       </c>
       <c r="R6" t="n">
-        <v>6738020</v>
+        <v>6737892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121348177</v>
+        <v>121346658</v>
       </c>
       <c r="B7" t="n">
-        <v>90662</v>
+        <v>74649</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,34 +1249,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435961</v>
+        <v>436188</v>
       </c>
       <c r="R7" t="n">
-        <v>6737833</v>
+        <v>6738012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347381</v>
+        <v>121346680</v>
       </c>
       <c r="B8" t="n">
-        <v>78635</v>
+        <v>78340</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,34 +1351,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435997</v>
+        <v>436183</v>
       </c>
       <c r="R8" t="n">
-        <v>6737899</v>
+        <v>6738020</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347142</v>
+        <v>121347315</v>
       </c>
       <c r="B9" t="n">
-        <v>78635</v>
+        <v>80561</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,34 +1453,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436148</v>
+        <v>436015</v>
       </c>
       <c r="R9" t="n">
-        <v>6737987</v>
+        <v>6737908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346617</v>
+        <v>121347321</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>90709</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436197</v>
+        <v>436013</v>
       </c>
       <c r="R10" t="n">
-        <v>6737992</v>
+        <v>6737929</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347953</v>
+        <v>121346569</v>
       </c>
       <c r="B11" t="n">
-        <v>100347</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,38 +1653,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435579</v>
+        <v>436212</v>
       </c>
       <c r="R11" t="n">
-        <v>6737637</v>
+        <v>6737992</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347321</v>
+        <v>121348302</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1768,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1792,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436013</v>
+        <v>436091</v>
       </c>
       <c r="R12" t="n">
-        <v>6737929</v>
+        <v>6737907</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347087</v>
+        <v>121347949</v>
       </c>
       <c r="B13" t="n">
-        <v>57504</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,47 +1857,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436159</v>
+        <v>435576</v>
       </c>
       <c r="R13" t="n">
-        <v>6737985</v>
+        <v>6737633</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347858</v>
+        <v>121347953</v>
       </c>
       <c r="B14" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435596</v>
+        <v>435579</v>
       </c>
       <c r="R14" t="n">
-        <v>6737662</v>
+        <v>6737637</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347315</v>
+        <v>121348117</v>
       </c>
       <c r="B15" t="n">
-        <v>80558</v>
+        <v>100360</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,25 +2070,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2107,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436015</v>
+        <v>435853</v>
       </c>
       <c r="R15" t="n">
-        <v>6737908</v>
+        <v>6737770</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346881</v>
+        <v>121347180</v>
       </c>
       <c r="B16" t="n">
-        <v>78635</v>
+        <v>79222</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2176,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2209,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436163</v>
+        <v>436132</v>
       </c>
       <c r="R16" t="n">
-        <v>6737990</v>
+        <v>6737977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347961</v>
+        <v>121348177</v>
       </c>
       <c r="B17" t="n">
-        <v>100347</v>
+        <v>90674</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,21 +2278,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435592</v>
+        <v>435961</v>
       </c>
       <c r="R17" t="n">
-        <v>6737627</v>
+        <v>6737833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347838</v>
+        <v>121346735</v>
       </c>
       <c r="B18" t="n">
-        <v>91137</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,38 +2376,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435602</v>
+        <v>436168</v>
       </c>
       <c r="R18" t="n">
-        <v>6737684</v>
+        <v>6737999</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347401</v>
+        <v>121347961</v>
       </c>
       <c r="B19" t="n">
-        <v>95375</v>
+        <v>100360</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2482,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2506,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435964</v>
+        <v>435592</v>
       </c>
       <c r="R19" t="n">
-        <v>6737892</v>
+        <v>6737627</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,10 +2568,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347503</v>
+        <v>121346617</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>79222</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2589,47 +2580,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435899</v>
+        <v>436197</v>
       </c>
       <c r="R20" t="n">
-        <v>6737841</v>
+        <v>6737992</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121348302</v>
+        <v>121347858</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>100360</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,38 +2682,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436091</v>
+        <v>435596</v>
       </c>
       <c r="R21" t="n">
-        <v>6737907</v>
+        <v>6737662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,10 +2772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121348221</v>
+        <v>121346682</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>78341</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2802,47 +2784,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435979</v>
+        <v>436183</v>
       </c>
       <c r="R22" t="n">
-        <v>6737851</v>
+        <v>6738020</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347949</v>
+        <v>121347170</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,47 +2886,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435576</v>
+        <v>436138</v>
       </c>
       <c r="R23" t="n">
-        <v>6737633</v>
+        <v>6737980</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121348117</v>
+        <v>121347836</v>
       </c>
       <c r="B24" t="n">
-        <v>100347</v>
+        <v>90709</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,25 +2988,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,10 +3016,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435853</v>
+        <v>435602</v>
       </c>
       <c r="R24" t="n">
-        <v>6737770</v>
+        <v>6737684</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347836</v>
+        <v>121347850</v>
       </c>
       <c r="B25" t="n">
-        <v>90697</v>
+        <v>94496</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3126,25 +3090,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3154,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435602</v>
+        <v>435603</v>
       </c>
       <c r="R25" t="n">
-        <v>6737684</v>
+        <v>6737665</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,10 +3180,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347180</v>
+        <v>121346787</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>78604</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3232,21 +3196,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3256,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436132</v>
+        <v>436175</v>
       </c>
       <c r="R26" t="n">
-        <v>6737977</v>
+        <v>6737983</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,10 +3282,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346680</v>
+        <v>121347087</v>
       </c>
       <c r="B27" t="n">
-        <v>78337</v>
+        <v>57504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3334,34 +3298,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436183</v>
+        <v>436159</v>
       </c>
       <c r="R27" t="n">
-        <v>6738020</v>
+        <v>6737985</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,10 +3393,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347170</v>
+        <v>121347275</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3432,38 +3405,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436138</v>
+        <v>436019</v>
       </c>
       <c r="R28" t="n">
-        <v>6737980</v>
+        <v>6737925</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,10 +3504,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347216</v>
+        <v>121347503</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>98094</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3534,38 +3516,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436129</v>
+        <v>435899</v>
       </c>
       <c r="R29" t="n">
-        <v>6737975</v>
+        <v>6737841</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,10 +3615,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347743</v>
+        <v>121347381</v>
       </c>
       <c r="B30" t="n">
-        <v>98081</v>
+        <v>78638</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3636,47 +3627,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435764</v>
+        <v>435997</v>
       </c>
       <c r="R30" t="n">
-        <v>6737744</v>
+        <v>6737899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,10 +3717,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121347759</v>
+        <v>121348221</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3747,38 +3729,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435691</v>
+        <v>435979</v>
       </c>
       <c r="R31" t="n">
-        <v>6737739</v>
+        <v>6737851</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,10 +3828,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347275</v>
+        <v>121347925</v>
       </c>
       <c r="B32" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3872,7 +3863,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3882,14 +3873,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436019</v>
+        <v>435579</v>
       </c>
       <c r="R32" t="n">
-        <v>6737925</v>
+        <v>6737662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3948,10 +3939,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121347412</v>
+        <v>121346697</v>
       </c>
       <c r="B33" t="n">
-        <v>98081</v>
+        <v>74649</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,47 +3951,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435964</v>
+        <v>436180</v>
       </c>
       <c r="R33" t="n">
-        <v>6737892</v>
+        <v>6737996</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121346735</v>
+        <v>121347743</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4071,38 +4053,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436168</v>
+        <v>435764</v>
       </c>
       <c r="R34" t="n">
-        <v>6737999</v>
+        <v>6737744</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346658</v>
+        <v>121347838</v>
       </c>
       <c r="B35" t="n">
-        <v>74647</v>
+        <v>91149</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4173,38 +4164,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436188</v>
+        <v>435602</v>
       </c>
       <c r="R35" t="n">
-        <v>6738012</v>
+        <v>6737684</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4263,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121348251</v>
+        <v>121347759</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4303,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436011</v>
+        <v>435691</v>
       </c>
       <c r="R36" t="n">
-        <v>6737862</v>
+        <v>6737739</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347850</v>
+        <v>121348251</v>
       </c>
       <c r="B37" t="n">
-        <v>94484</v>
+        <v>78604</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4377,25 +4368,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4405,10 +4396,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435603</v>
+        <v>436011</v>
       </c>
       <c r="R37" t="n">
-        <v>6737665</v>
+        <v>6737862</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121346787</v>
+        <v>121347826</v>
       </c>
       <c r="B38" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4479,38 +4470,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436175</v>
+        <v>435632</v>
       </c>
       <c r="R38" t="n">
-        <v>6737983</v>
+        <v>6737702</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346697</v>
+        <v>121347412</v>
       </c>
       <c r="B39" t="n">
-        <v>74647</v>
+        <v>98094</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4581,38 +4581,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436180</v>
+        <v>435964</v>
       </c>
       <c r="R39" t="n">
-        <v>6737996</v>
+        <v>6737892</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121347826</v>
+        <v>121347216</v>
       </c>
       <c r="B40" t="n">
-        <v>98081</v>
+        <v>79222</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4683,47 +4692,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435632</v>
+        <v>436129</v>
       </c>
       <c r="R40" t="n">
-        <v>6737702</v>
+        <v>6737975</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374891</v>
+        <v>121374888</v>
       </c>
       <c r="B41" t="n">
-        <v>100256</v>
+        <v>91392</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222771</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435907</v>
+        <v>435889</v>
       </c>
       <c r="R41" t="n">
-        <v>6737812</v>
+        <v>6737827</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4866,7 +4866,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4885,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374885</v>
+        <v>121374879</v>
       </c>
       <c r="B42" t="n">
-        <v>98417</v>
+        <v>91642</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4901,21 +4900,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219880</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4925,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435878</v>
+        <v>435838</v>
       </c>
       <c r="R42" t="n">
-        <v>6737810</v>
+        <v>6737809</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,10 +4986,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374882</v>
+        <v>121374891</v>
       </c>
       <c r="B43" t="n">
-        <v>90711</v>
+        <v>100269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4999,25 +4998,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>222771</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435870</v>
+        <v>435907</v>
       </c>
       <c r="R43" t="n">
-        <v>6737805</v>
+        <v>6737812</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5071,6 +5070,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374889</v>
+        <v>121374886</v>
       </c>
       <c r="B44" t="n">
-        <v>91985</v>
+        <v>91987</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5101,25 +5101,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>788</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435889</v>
+        <v>435868</v>
       </c>
       <c r="R44" t="n">
-        <v>6737819</v>
+        <v>6737835</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374886</v>
+        <v>121374889</v>
       </c>
       <c r="B45" t="n">
-        <v>91975</v>
+        <v>91997</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,25 +5203,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>788</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435868</v>
+        <v>435889</v>
       </c>
       <c r="R45" t="n">
-        <v>6737835</v>
+        <v>6737819</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374881</v>
+        <v>121374883</v>
       </c>
       <c r="B46" t="n">
-        <v>92004</v>
+        <v>91642</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435851</v>
+        <v>435879</v>
       </c>
       <c r="R46" t="n">
-        <v>6737817</v>
+        <v>6737803</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374892</v>
+        <v>121374885</v>
       </c>
       <c r="B47" t="n">
-        <v>95375</v>
+        <v>98430</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2869</v>
+        <v>219880</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435973</v>
+        <v>435878</v>
       </c>
       <c r="R47" t="n">
-        <v>6737875</v>
+        <v>6737810</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374883</v>
+        <v>121374882</v>
       </c>
       <c r="B48" t="n">
-        <v>91630</v>
+        <v>90723</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435879</v>
+        <v>435870</v>
       </c>
       <c r="R48" t="n">
-        <v>6737803</v>
+        <v>6737805</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374888</v>
+        <v>121374881</v>
       </c>
       <c r="B49" t="n">
-        <v>91380</v>
+        <v>92016</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,25 +5611,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>1968</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435889</v>
+        <v>435851</v>
       </c>
       <c r="R49" t="n">
-        <v>6737827</v>
+        <v>6737817</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374899</v>
+        <v>121374892</v>
       </c>
       <c r="B50" t="n">
-        <v>91981</v>
+        <v>95388</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2058</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436217</v>
+        <v>435973</v>
       </c>
       <c r="R50" t="n">
-        <v>6737988</v>
+        <v>6737875</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374879</v>
+        <v>121374899</v>
       </c>
       <c r="B51" t="n">
-        <v>91630</v>
+        <v>91993</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5815,25 +5815,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>2058</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435838</v>
+        <v>436217</v>
       </c>
       <c r="R51" t="n">
-        <v>6737809</v>
+        <v>6737988</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346881</v>
+        <v>121348302</v>
       </c>
       <c r="B4" t="n">
-        <v>78638</v>
+        <v>78604</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436163</v>
+        <v>436091</v>
       </c>
       <c r="R4" t="n">
-        <v>6737990</v>
+        <v>6737907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347142</v>
+        <v>121347412</v>
       </c>
       <c r="B5" t="n">
-        <v>78638</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1041,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436148</v>
+        <v>435964</v>
       </c>
       <c r="R5" t="n">
-        <v>6737987</v>
+        <v>6737892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347401</v>
+        <v>121347858</v>
       </c>
       <c r="B6" t="n">
-        <v>95388</v>
+        <v>100361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435964</v>
+        <v>435596</v>
       </c>
       <c r="R6" t="n">
-        <v>6737892</v>
+        <v>6737662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346658</v>
+        <v>121347850</v>
       </c>
       <c r="B7" t="n">
-        <v>74649</v>
+        <v>94497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,34 +1258,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436188</v>
+        <v>435603</v>
       </c>
       <c r="R7" t="n">
-        <v>6738012</v>
+        <v>6737665</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346680</v>
+        <v>121347180</v>
       </c>
       <c r="B8" t="n">
-        <v>78340</v>
+        <v>79222</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436183</v>
+        <v>436132</v>
       </c>
       <c r="R8" t="n">
-        <v>6738020</v>
+        <v>6737977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347315</v>
+        <v>121347275</v>
       </c>
       <c r="B9" t="n">
-        <v>80561</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,38 +1458,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436015</v>
+        <v>436019</v>
       </c>
       <c r="R9" t="n">
-        <v>6737908</v>
+        <v>6737925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347321</v>
+        <v>121347826</v>
       </c>
       <c r="B10" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,38 +1569,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436013</v>
+        <v>435632</v>
       </c>
       <c r="R10" t="n">
-        <v>6737929</v>
+        <v>6737702</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346569</v>
+        <v>121347925</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,38 +1680,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436212</v>
+        <v>435579</v>
       </c>
       <c r="R11" t="n">
-        <v>6737992</v>
+        <v>6737662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1779,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121348302</v>
+        <v>121347315</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>80561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,34 +1795,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436091</v>
+        <v>436015</v>
       </c>
       <c r="R12" t="n">
-        <v>6737907</v>
+        <v>6737908</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347949</v>
+        <v>121347087</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>57504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,47 +1893,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435576</v>
+        <v>436159</v>
       </c>
       <c r="R13" t="n">
-        <v>6737633</v>
+        <v>6737985</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347953</v>
+        <v>121347503</v>
       </c>
       <c r="B14" t="n">
-        <v>100360</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,38 +2004,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435579</v>
+        <v>435899</v>
       </c>
       <c r="R14" t="n">
-        <v>6737637</v>
+        <v>6737841</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,10 +2103,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121348117</v>
+        <v>121347142</v>
       </c>
       <c r="B15" t="n">
-        <v>100360</v>
+        <v>78638</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,38 +2115,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435853</v>
+        <v>436148</v>
       </c>
       <c r="R15" t="n">
-        <v>6737770</v>
+        <v>6737987</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347180</v>
+        <v>121347836</v>
       </c>
       <c r="B16" t="n">
-        <v>79222</v>
+        <v>90710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,34 +2221,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436132</v>
+        <v>435602</v>
       </c>
       <c r="R16" t="n">
-        <v>6737977</v>
+        <v>6737684</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121348177</v>
+        <v>121348221</v>
       </c>
       <c r="B17" t="n">
-        <v>90674</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,38 +2319,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435961</v>
+        <v>435979</v>
       </c>
       <c r="R17" t="n">
-        <v>6737833</v>
+        <v>6737851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2364,10 +2418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346735</v>
+        <v>121347949</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2376,38 +2430,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436168</v>
+        <v>435576</v>
       </c>
       <c r="R18" t="n">
-        <v>6737999</v>
+        <v>6737633</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,10 +2529,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347961</v>
+        <v>121348251</v>
       </c>
       <c r="B19" t="n">
-        <v>100360</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2478,25 +2541,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2506,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435592</v>
+        <v>436011</v>
       </c>
       <c r="R19" t="n">
-        <v>6737627</v>
+        <v>6737862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346617</v>
+        <v>121347838</v>
       </c>
       <c r="B20" t="n">
-        <v>79222</v>
+        <v>91150</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2580,38 +2643,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436197</v>
+        <v>435602</v>
       </c>
       <c r="R20" t="n">
-        <v>6737992</v>
+        <v>6737684</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,10 +2733,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347858</v>
+        <v>121347170</v>
       </c>
       <c r="B21" t="n">
-        <v>100360</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2682,38 +2745,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435596</v>
+        <v>436138</v>
       </c>
       <c r="R21" t="n">
-        <v>6737662</v>
+        <v>6737980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2772,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121346682</v>
+        <v>121347953</v>
       </c>
       <c r="B22" t="n">
-        <v>78341</v>
+        <v>100361</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2784,38 +2847,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436183</v>
+        <v>435579</v>
       </c>
       <c r="R22" t="n">
-        <v>6738020</v>
+        <v>6737637</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347170</v>
+        <v>121346682</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>78341</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2914,10 +2977,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436138</v>
+        <v>436183</v>
       </c>
       <c r="R23" t="n">
-        <v>6737980</v>
+        <v>6738020</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2976,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347836</v>
+        <v>121347961</v>
       </c>
       <c r="B24" t="n">
-        <v>90709</v>
+        <v>100361</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2988,25 +3051,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3016,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435602</v>
+        <v>435592</v>
       </c>
       <c r="R24" t="n">
-        <v>6737684</v>
+        <v>6737627</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3078,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347850</v>
+        <v>121347216</v>
       </c>
       <c r="B25" t="n">
-        <v>94496</v>
+        <v>79222</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,38 +3153,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435603</v>
+        <v>436129</v>
       </c>
       <c r="R25" t="n">
-        <v>6737665</v>
+        <v>6737975</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,10 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346787</v>
+        <v>121347321</v>
       </c>
       <c r="B26" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3196,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436175</v>
+        <v>436013</v>
       </c>
       <c r="R26" t="n">
-        <v>6737983</v>
+        <v>6737929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347087</v>
+        <v>121346569</v>
       </c>
       <c r="B27" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3298,43 +3361,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436159</v>
+        <v>436212</v>
       </c>
       <c r="R27" t="n">
-        <v>6737985</v>
+        <v>6737992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3393,10 +3447,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347275</v>
+        <v>121346881</v>
       </c>
       <c r="B28" t="n">
-        <v>98094</v>
+        <v>78638</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3405,47 +3459,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436019</v>
+        <v>436163</v>
       </c>
       <c r="R28" t="n">
-        <v>6737925</v>
+        <v>6737990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3504,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347503</v>
+        <v>121347401</v>
       </c>
       <c r="B29" t="n">
-        <v>98094</v>
+        <v>95389</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3516,47 +3561,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435899</v>
+        <v>435964</v>
       </c>
       <c r="R29" t="n">
-        <v>6737841</v>
+        <v>6737892</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347381</v>
+        <v>121346697</v>
       </c>
       <c r="B30" t="n">
-        <v>78638</v>
+        <v>74649</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3627,38 +3663,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435997</v>
+        <v>436180</v>
       </c>
       <c r="R30" t="n">
-        <v>6737899</v>
+        <v>6737996</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121348221</v>
+        <v>121346735</v>
       </c>
       <c r="B31" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3729,47 +3765,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435979</v>
+        <v>436168</v>
       </c>
       <c r="R31" t="n">
-        <v>6737851</v>
+        <v>6737999</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347925</v>
+        <v>121346787</v>
       </c>
       <c r="B32" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3840,47 +3867,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435579</v>
+        <v>436175</v>
       </c>
       <c r="R32" t="n">
-        <v>6737662</v>
+        <v>6737983</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3939,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121346697</v>
+        <v>121348117</v>
       </c>
       <c r="B33" t="n">
-        <v>74649</v>
+        <v>100361</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3955,34 +3973,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436180</v>
+        <v>435853</v>
       </c>
       <c r="R33" t="n">
-        <v>6737996</v>
+        <v>6737770</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4044,7 +4062,7 @@
         <v>121347743</v>
       </c>
       <c r="B34" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4152,10 +4170,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347838</v>
+        <v>121346617</v>
       </c>
       <c r="B35" t="n">
-        <v>91149</v>
+        <v>79222</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,38 +4182,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435602</v>
+        <v>436197</v>
       </c>
       <c r="R35" t="n">
-        <v>6737684</v>
+        <v>6737992</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,10 +4272,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121347759</v>
+        <v>121346658</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
+        <v>74649</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,38 +4284,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435691</v>
+        <v>436188</v>
       </c>
       <c r="R36" t="n">
-        <v>6737739</v>
+        <v>6738012</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121348251</v>
+        <v>121346680</v>
       </c>
       <c r="B37" t="n">
-        <v>78604</v>
+        <v>78340</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4372,34 +4390,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436011</v>
+        <v>436183</v>
       </c>
       <c r="R37" t="n">
-        <v>6737862</v>
+        <v>6738020</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347826</v>
+        <v>121348177</v>
       </c>
       <c r="B38" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4470,47 +4488,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435632</v>
+        <v>435961</v>
       </c>
       <c r="R38" t="n">
-        <v>6737702</v>
+        <v>6737833</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121347412</v>
+        <v>121347381</v>
       </c>
       <c r="B39" t="n">
-        <v>98094</v>
+        <v>78638</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4581,47 +4590,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435964</v>
+        <v>435997</v>
       </c>
       <c r="R39" t="n">
-        <v>6737892</v>
+        <v>6737899</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121347216</v>
+        <v>121347759</v>
       </c>
       <c r="B40" t="n">
-        <v>79222</v>
+        <v>78604</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4696,34 +4696,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436129</v>
+        <v>435691</v>
       </c>
       <c r="R40" t="n">
-        <v>6737975</v>
+        <v>6737739</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374888</v>
+        <v>121374883</v>
       </c>
       <c r="B41" t="n">
-        <v>91392</v>
+        <v>91643</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435889</v>
+        <v>435879</v>
       </c>
       <c r="R41" t="n">
-        <v>6737827</v>
+        <v>6737803</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374879</v>
+        <v>121374891</v>
       </c>
       <c r="B42" t="n">
-        <v>91642</v>
+        <v>100270</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435838</v>
+        <v>435907</v>
       </c>
       <c r="R42" t="n">
-        <v>6737809</v>
+        <v>6737812</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4968,6 +4968,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4986,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374891</v>
+        <v>121374892</v>
       </c>
       <c r="B43" t="n">
-        <v>100269</v>
+        <v>95389</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5002,21 +5003,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222771</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435907</v>
+        <v>435973</v>
       </c>
       <c r="R43" t="n">
-        <v>6737812</v>
+        <v>6737875</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5070,7 +5071,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374886</v>
+        <v>121374879</v>
       </c>
       <c r="B44" t="n">
-        <v>91987</v>
+        <v>91643</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5101,25 +5101,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435868</v>
+        <v>435838</v>
       </c>
       <c r="R44" t="n">
-        <v>6737835</v>
+        <v>6737809</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374889</v>
+        <v>121374881</v>
       </c>
       <c r="B45" t="n">
-        <v>91997</v>
+        <v>92017</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,25 +5203,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>1968</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435889</v>
+        <v>435851</v>
       </c>
       <c r="R45" t="n">
-        <v>6737819</v>
+        <v>6737817</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374883</v>
+        <v>121374899</v>
       </c>
       <c r="B46" t="n">
-        <v>91642</v>
+        <v>91994</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>2058</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435879</v>
+        <v>436217</v>
       </c>
       <c r="R46" t="n">
-        <v>6737803</v>
+        <v>6737988</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5398,7 +5398,7 @@
         <v>121374885</v>
       </c>
       <c r="B47" t="n">
-        <v>98430</v>
+        <v>98431</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>121374882</v>
       </c>
       <c r="B48" t="n">
-        <v>90723</v>
+        <v>90724</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374881</v>
+        <v>121374888</v>
       </c>
       <c r="B49" t="n">
-        <v>92016</v>
+        <v>91393</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,25 +5611,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435851</v>
+        <v>435889</v>
       </c>
       <c r="R49" t="n">
-        <v>6737817</v>
+        <v>6737827</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374892</v>
+        <v>121374886</v>
       </c>
       <c r="B50" t="n">
-        <v>95388</v>
+        <v>91988</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>788</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435973</v>
+        <v>435868</v>
       </c>
       <c r="R50" t="n">
-        <v>6737875</v>
+        <v>6737835</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374899</v>
+        <v>121374889</v>
       </c>
       <c r="B51" t="n">
-        <v>91993</v>
+        <v>91998</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5815,25 +5815,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2058</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436217</v>
+        <v>435889</v>
       </c>
       <c r="R51" t="n">
-        <v>6737988</v>
+        <v>6737819</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121348302</v>
+        <v>121347953</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
+        <v>100364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,38 +939,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436091</v>
+        <v>435579</v>
       </c>
       <c r="R4" t="n">
-        <v>6737907</v>
+        <v>6737637</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347412</v>
+        <v>121346787</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,47 +1041,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435964</v>
+        <v>436175</v>
       </c>
       <c r="R5" t="n">
-        <v>6737892</v>
+        <v>6737983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347858</v>
+        <v>121347170</v>
       </c>
       <c r="B6" t="n">
-        <v>100361</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1143,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435596</v>
+        <v>436138</v>
       </c>
       <c r="R6" t="n">
-        <v>6737662</v>
+        <v>6737980</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347850</v>
+        <v>121347836</v>
       </c>
       <c r="B7" t="n">
-        <v>94497</v>
+        <v>90713</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435603</v>
+        <v>435602</v>
       </c>
       <c r="R7" t="n">
-        <v>6737665</v>
+        <v>6737684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347180</v>
+        <v>121347321</v>
       </c>
       <c r="B8" t="n">
-        <v>79222</v>
+        <v>90713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436132</v>
+        <v>436013</v>
       </c>
       <c r="R8" t="n">
-        <v>6737977</v>
+        <v>6737929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347275</v>
+        <v>121347412</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,7 +1472,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1491,14 +1482,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436019</v>
+        <v>435964</v>
       </c>
       <c r="R9" t="n">
-        <v>6737925</v>
+        <v>6737892</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347826</v>
+        <v>121347180</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>79225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,47 +1560,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435632</v>
+        <v>436132</v>
       </c>
       <c r="R10" t="n">
-        <v>6737702</v>
+        <v>6737977</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347925</v>
+        <v>121347381</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>78641</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,47 +1662,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435579</v>
+        <v>435997</v>
       </c>
       <c r="R11" t="n">
-        <v>6737662</v>
+        <v>6737899</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1779,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347315</v>
+        <v>121347142</v>
       </c>
       <c r="B12" t="n">
-        <v>80561</v>
+        <v>78641</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1795,34 +1768,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436015</v>
+        <v>436148</v>
       </c>
       <c r="R12" t="n">
-        <v>6737908</v>
+        <v>6737987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347087</v>
+        <v>121347850</v>
       </c>
       <c r="B13" t="n">
-        <v>57504</v>
+        <v>94500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,47 +1866,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436159</v>
+        <v>435603</v>
       </c>
       <c r="R13" t="n">
-        <v>6737985</v>
+        <v>6737665</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347503</v>
+        <v>121347216</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>79225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,47 +1968,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435899</v>
+        <v>436129</v>
       </c>
       <c r="R14" t="n">
-        <v>6737841</v>
+        <v>6737975</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,10 +2058,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347142</v>
+        <v>121347858</v>
       </c>
       <c r="B15" t="n">
-        <v>78638</v>
+        <v>100364</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2115,38 +2070,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436148</v>
+        <v>435596</v>
       </c>
       <c r="R15" t="n">
-        <v>6737987</v>
+        <v>6737662</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2205,10 +2160,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347836</v>
+        <v>121348177</v>
       </c>
       <c r="B16" t="n">
-        <v>90710</v>
+        <v>90678</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,25 +2172,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2245,10 +2200,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435602</v>
+        <v>435961</v>
       </c>
       <c r="R16" t="n">
-        <v>6737684</v>
+        <v>6737833</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121348221</v>
+        <v>121347826</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,7 +2297,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2356,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435979</v>
+        <v>435632</v>
       </c>
       <c r="R17" t="n">
-        <v>6737851</v>
+        <v>6737702</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347949</v>
+        <v>121348251</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2430,47 +2385,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435576</v>
+        <v>436011</v>
       </c>
       <c r="R18" t="n">
-        <v>6737633</v>
+        <v>6737862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121348251</v>
+        <v>121347401</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>95392</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,25 +2487,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436011</v>
+        <v>435964</v>
       </c>
       <c r="R19" t="n">
-        <v>6737862</v>
+        <v>6737892</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347838</v>
+        <v>121346881</v>
       </c>
       <c r="B20" t="n">
-        <v>91150</v>
+        <v>78641</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,38 +2589,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435602</v>
+        <v>436163</v>
       </c>
       <c r="R20" t="n">
-        <v>6737684</v>
+        <v>6737990</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,10 +2679,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347170</v>
+        <v>121347275</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2745,38 +2691,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436138</v>
+        <v>436019</v>
       </c>
       <c r="R21" t="n">
-        <v>6737980</v>
+        <v>6737925</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2835,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347953</v>
+        <v>121346680</v>
       </c>
       <c r="B22" t="n">
-        <v>100361</v>
+        <v>78343</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,38 +2802,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435579</v>
+        <v>436183</v>
       </c>
       <c r="R22" t="n">
-        <v>6737637</v>
+        <v>6738020</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2937,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346682</v>
+        <v>121346735</v>
       </c>
       <c r="B23" t="n">
-        <v>78341</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436183</v>
+        <v>436168</v>
       </c>
       <c r="R23" t="n">
-        <v>6738020</v>
+        <v>6737999</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347961</v>
+        <v>121347743</v>
       </c>
       <c r="B24" t="n">
-        <v>100361</v>
+        <v>98098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,38 +3006,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435592</v>
+        <v>435764</v>
       </c>
       <c r="R24" t="n">
-        <v>6737627</v>
+        <v>6737744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,10 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347216</v>
+        <v>121347503</v>
       </c>
       <c r="B25" t="n">
-        <v>79222</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,38 +3117,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436129</v>
+        <v>435899</v>
       </c>
       <c r="R25" t="n">
-        <v>6737975</v>
+        <v>6737841</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347321</v>
+        <v>121347838</v>
       </c>
       <c r="B26" t="n">
-        <v>90710</v>
+        <v>91153</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3255,38 +3228,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436013</v>
+        <v>435602</v>
       </c>
       <c r="R26" t="n">
-        <v>6737929</v>
+        <v>6737684</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346569</v>
+        <v>121348117</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>100364</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3357,38 +3330,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436212</v>
+        <v>435853</v>
       </c>
       <c r="R27" t="n">
-        <v>6737992</v>
+        <v>6737770</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,10 +3420,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346881</v>
+        <v>121346569</v>
       </c>
       <c r="B28" t="n">
-        <v>78638</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,21 +3436,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3487,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436163</v>
+        <v>436212</v>
       </c>
       <c r="R28" t="n">
-        <v>6737990</v>
+        <v>6737992</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3549,10 +3522,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347401</v>
+        <v>121347087</v>
       </c>
       <c r="B29" t="n">
-        <v>95389</v>
+        <v>57507</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3561,38 +3534,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435964</v>
+        <v>436159</v>
       </c>
       <c r="R29" t="n">
-        <v>6737892</v>
+        <v>6737985</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121346697</v>
+        <v>121348302</v>
       </c>
       <c r="B30" t="n">
-        <v>74649</v>
+        <v>78607</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3663,25 +3645,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3673,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436180</v>
+        <v>436091</v>
       </c>
       <c r="R30" t="n">
-        <v>6737996</v>
+        <v>6737907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346735</v>
+        <v>121348221</v>
       </c>
       <c r="B31" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3765,38 +3747,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436168</v>
+        <v>435979</v>
       </c>
       <c r="R31" t="n">
-        <v>6737999</v>
+        <v>6737851</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346787</v>
+        <v>121347949</v>
       </c>
       <c r="B32" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3867,38 +3858,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436175</v>
+        <v>435576</v>
       </c>
       <c r="R32" t="n">
-        <v>6737983</v>
+        <v>6737633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121348117</v>
+        <v>121347315</v>
       </c>
       <c r="B33" t="n">
-        <v>100361</v>
+        <v>80564</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3969,25 +3969,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435853</v>
+        <v>436015</v>
       </c>
       <c r="R33" t="n">
-        <v>6737770</v>
+        <v>6737908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,10 +4059,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347743</v>
+        <v>121346682</v>
       </c>
       <c r="B34" t="n">
-        <v>98095</v>
+        <v>78344</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4071,47 +4071,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435764</v>
+        <v>436183</v>
       </c>
       <c r="R34" t="n">
-        <v>6737744</v>
+        <v>6738020</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4170,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121346617</v>
+        <v>121347961</v>
       </c>
       <c r="B35" t="n">
-        <v>79222</v>
+        <v>100364</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4182,38 +4173,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436197</v>
+        <v>435592</v>
       </c>
       <c r="R35" t="n">
-        <v>6737992</v>
+        <v>6737627</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,7 +4266,7 @@
         <v>121346658</v>
       </c>
       <c r="B36" t="n">
-        <v>74649</v>
+        <v>74652</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4374,10 +4365,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346680</v>
+        <v>121346697</v>
       </c>
       <c r="B37" t="n">
-        <v>78340</v>
+        <v>74652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4386,25 +4377,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,10 +4405,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436183</v>
+        <v>436180</v>
       </c>
       <c r="R37" t="n">
-        <v>6738020</v>
+        <v>6737996</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,10 +4467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121348177</v>
+        <v>121347759</v>
       </c>
       <c r="B38" t="n">
-        <v>90675</v>
+        <v>78607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4488,25 +4479,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4516,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435961</v>
+        <v>435691</v>
       </c>
       <c r="R38" t="n">
-        <v>6737833</v>
+        <v>6737739</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121347381</v>
+        <v>121347925</v>
       </c>
       <c r="B39" t="n">
-        <v>78638</v>
+        <v>98098</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4590,38 +4581,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435997</v>
+        <v>435579</v>
       </c>
       <c r="R39" t="n">
-        <v>6737899</v>
+        <v>6737662</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121347759</v>
+        <v>121346617</v>
       </c>
       <c r="B40" t="n">
-        <v>78604</v>
+        <v>79225</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4696,34 +4696,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435691</v>
+        <v>436197</v>
       </c>
       <c r="R40" t="n">
-        <v>6737739</v>
+        <v>6737992</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374883</v>
+        <v>121374888</v>
       </c>
       <c r="B41" t="n">
-        <v>91643</v>
+        <v>91396</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435879</v>
+        <v>435889</v>
       </c>
       <c r="R41" t="n">
-        <v>6737803</v>
+        <v>6737827</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374891</v>
+        <v>121374881</v>
       </c>
       <c r="B42" t="n">
-        <v>100270</v>
+        <v>92020</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>1968</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435907</v>
+        <v>435851</v>
       </c>
       <c r="R42" t="n">
-        <v>6737812</v>
+        <v>6737817</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4968,7 +4968,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>121374892</v>
       </c>
       <c r="B43" t="n">
-        <v>95389</v>
+        <v>95392</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5089,10 +5088,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374879</v>
+        <v>121374899</v>
       </c>
       <c r="B44" t="n">
-        <v>91643</v>
+        <v>91997</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5101,25 +5100,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>2058</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5128,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435838</v>
+        <v>436217</v>
       </c>
       <c r="R44" t="n">
-        <v>6737809</v>
+        <v>6737988</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5191,10 +5190,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374881</v>
+        <v>121374886</v>
       </c>
       <c r="B45" t="n">
-        <v>92017</v>
+        <v>91991</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5207,21 +5206,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1968</v>
+        <v>788</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5230,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435851</v>
+        <v>435868</v>
       </c>
       <c r="R45" t="n">
-        <v>6737817</v>
+        <v>6737835</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5292,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374899</v>
+        <v>121374885</v>
       </c>
       <c r="B46" t="n">
-        <v>91994</v>
+        <v>98434</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5304,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2058</v>
+        <v>219880</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5332,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436217</v>
+        <v>435878</v>
       </c>
       <c r="R46" t="n">
-        <v>6737988</v>
+        <v>6737810</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5394,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374885</v>
+        <v>121374889</v>
       </c>
       <c r="B47" t="n">
-        <v>98431</v>
+        <v>92001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5410,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219880</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5434,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435878</v>
+        <v>435889</v>
       </c>
       <c r="R47" t="n">
-        <v>6737810</v>
+        <v>6737819</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5500,7 +5499,7 @@
         <v>121374882</v>
       </c>
       <c r="B48" t="n">
-        <v>90724</v>
+        <v>90727</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,10 +5598,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374888</v>
+        <v>121374891</v>
       </c>
       <c r="B49" t="n">
-        <v>91393</v>
+        <v>100273</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,21 +5614,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>222771</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5638,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435889</v>
+        <v>435907</v>
       </c>
       <c r="R49" t="n">
-        <v>6737827</v>
+        <v>6737812</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5683,6 +5682,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374886</v>
+        <v>121374883</v>
       </c>
       <c r="B50" t="n">
-        <v>91988</v>
+        <v>91646</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435868</v>
+        <v>435879</v>
       </c>
       <c r="R50" t="n">
-        <v>6737835</v>
+        <v>6737803</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374889</v>
+        <v>121374879</v>
       </c>
       <c r="B51" t="n">
-        <v>91998</v>
+        <v>91646</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435889</v>
+        <v>435838</v>
       </c>
       <c r="R51" t="n">
-        <v>6737819</v>
+        <v>6737809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347953</v>
+        <v>121347743</v>
       </c>
       <c r="B4" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,38 +939,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435579</v>
+        <v>435764</v>
       </c>
       <c r="R4" t="n">
-        <v>6737637</v>
+        <v>6737744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346787</v>
+        <v>121347503</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1050,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436175</v>
+        <v>435899</v>
       </c>
       <c r="R5" t="n">
-        <v>6737983</v>
+        <v>6737841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347170</v>
+        <v>121347759</v>
       </c>
       <c r="B6" t="n">
         <v>78607</v>
@@ -1167,14 +1185,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436138</v>
+        <v>435691</v>
       </c>
       <c r="R6" t="n">
-        <v>6737980</v>
+        <v>6737739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347836</v>
+        <v>121347838</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
+        <v>91153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1263,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1335,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347321</v>
+        <v>121348302</v>
       </c>
       <c r="B8" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,21 +1369,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436013</v>
+        <v>436091</v>
       </c>
       <c r="R8" t="n">
-        <v>6737929</v>
+        <v>6737907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1548,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347180</v>
+        <v>121347858</v>
       </c>
       <c r="B10" t="n">
-        <v>79225</v>
+        <v>100364</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,38 +1578,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436132</v>
+        <v>435596</v>
       </c>
       <c r="R10" t="n">
-        <v>6737977</v>
+        <v>6737662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1668,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347381</v>
+        <v>121347142</v>
       </c>
       <c r="B11" t="n">
         <v>78641</v>
@@ -1686,14 +1704,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435997</v>
+        <v>436148</v>
       </c>
       <c r="R11" t="n">
-        <v>6737899</v>
+        <v>6737987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347142</v>
+        <v>121347961</v>
       </c>
       <c r="B12" t="n">
-        <v>78641</v>
+        <v>100364</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,38 +1782,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436148</v>
+        <v>435592</v>
       </c>
       <c r="R12" t="n">
-        <v>6737987</v>
+        <v>6737627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347850</v>
+        <v>121346735</v>
       </c>
       <c r="B13" t="n">
-        <v>94500</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,38 +1884,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435603</v>
+        <v>436168</v>
       </c>
       <c r="R13" t="n">
-        <v>6737665</v>
+        <v>6737999</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347216</v>
+        <v>121347275</v>
       </c>
       <c r="B14" t="n">
-        <v>79225</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,38 +1986,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436129</v>
+        <v>436019</v>
       </c>
       <c r="R14" t="n">
-        <v>6737975</v>
+        <v>6737925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2085,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347858</v>
+        <v>121347953</v>
       </c>
       <c r="B15" t="n">
         <v>100364</v>
@@ -2098,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435596</v>
+        <v>435579</v>
       </c>
       <c r="R15" t="n">
-        <v>6737662</v>
+        <v>6737637</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121348177</v>
+        <v>121346617</v>
       </c>
       <c r="B16" t="n">
-        <v>90678</v>
+        <v>79225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,38 +2199,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435961</v>
+        <v>436197</v>
       </c>
       <c r="R16" t="n">
-        <v>6737833</v>
+        <v>6737992</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347826</v>
+        <v>121347401</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>95392</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2274,47 +2301,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435632</v>
+        <v>435964</v>
       </c>
       <c r="R17" t="n">
-        <v>6737702</v>
+        <v>6737892</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121348251</v>
+        <v>121348117</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>100364</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,25 +2403,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436011</v>
+        <v>435853</v>
       </c>
       <c r="R18" t="n">
-        <v>6737862</v>
+        <v>6737770</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347401</v>
+        <v>121348177</v>
       </c>
       <c r="B19" t="n">
-        <v>95392</v>
+        <v>90678</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,21 +2509,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435964</v>
+        <v>435961</v>
       </c>
       <c r="R19" t="n">
-        <v>6737892</v>
+        <v>6737833</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346881</v>
+        <v>121346787</v>
       </c>
       <c r="B20" t="n">
-        <v>78641</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2593,21 +2611,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2617,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436163</v>
+        <v>436175</v>
       </c>
       <c r="R20" t="n">
-        <v>6737990</v>
+        <v>6737983</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347275</v>
+        <v>121348251</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,47 +2709,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436019</v>
+        <v>436011</v>
       </c>
       <c r="R21" t="n">
-        <v>6737925</v>
+        <v>6737862</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121346680</v>
+        <v>121346881</v>
       </c>
       <c r="B22" t="n">
-        <v>78343</v>
+        <v>78641</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2815,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436183</v>
+        <v>436163</v>
       </c>
       <c r="R22" t="n">
-        <v>6738020</v>
+        <v>6737990</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346735</v>
+        <v>121347180</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>79225</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436168</v>
+        <v>436132</v>
       </c>
       <c r="R23" t="n">
-        <v>6737999</v>
+        <v>6737977</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347743</v>
+        <v>121347850</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>94500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3006,47 +3015,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435764</v>
+        <v>435603</v>
       </c>
       <c r="R24" t="n">
-        <v>6737744</v>
+        <v>6737665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,10 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347503</v>
+        <v>121346682</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>78344</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,47 +3117,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435899</v>
+        <v>436183</v>
       </c>
       <c r="R25" t="n">
-        <v>6737841</v>
+        <v>6738020</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347838</v>
+        <v>121347315</v>
       </c>
       <c r="B26" t="n">
-        <v>91153</v>
+        <v>80564</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3228,25 +3219,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3256,10 +3247,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435602</v>
+        <v>436015</v>
       </c>
       <c r="R26" t="n">
-        <v>6737684</v>
+        <v>6737908</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,10 +3309,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121348117</v>
+        <v>121347836</v>
       </c>
       <c r="B27" t="n">
-        <v>100364</v>
+        <v>90713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3330,25 +3321,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3358,10 +3349,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435853</v>
+        <v>435602</v>
       </c>
       <c r="R27" t="n">
-        <v>6737770</v>
+        <v>6737684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,10 +3411,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346569</v>
+        <v>121346658</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>74652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3432,25 +3423,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3460,10 +3451,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436212</v>
+        <v>436188</v>
       </c>
       <c r="R28" t="n">
-        <v>6737992</v>
+        <v>6738012</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347087</v>
+        <v>121346697</v>
       </c>
       <c r="B29" t="n">
-        <v>57507</v>
+        <v>74652</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3534,47 +3525,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436159</v>
+        <v>436180</v>
       </c>
       <c r="R29" t="n">
-        <v>6737985</v>
+        <v>6737996</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,10 +3615,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121348302</v>
+        <v>121347949</v>
       </c>
       <c r="B30" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3645,38 +3627,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436091</v>
+        <v>435576</v>
       </c>
       <c r="R30" t="n">
-        <v>6737907</v>
+        <v>6737633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,10 +3726,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121348221</v>
+        <v>121347321</v>
       </c>
       <c r="B31" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3747,47 +3738,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435979</v>
+        <v>436013</v>
       </c>
       <c r="R31" t="n">
-        <v>6737851</v>
+        <v>6737929</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,10 +3828,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347949</v>
+        <v>121347087</v>
       </c>
       <c r="B32" t="n">
-        <v>98098</v>
+        <v>57507</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,47 +3840,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435576</v>
+        <v>436159</v>
       </c>
       <c r="R32" t="n">
-        <v>6737633</v>
+        <v>6737985</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,10 +3939,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121347315</v>
+        <v>121348221</v>
       </c>
       <c r="B33" t="n">
-        <v>80564</v>
+        <v>98098</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3969,38 +3951,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436015</v>
+        <v>435979</v>
       </c>
       <c r="R33" t="n">
-        <v>6737908</v>
+        <v>6737851</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,10 +4050,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121346682</v>
+        <v>121347216</v>
       </c>
       <c r="B34" t="n">
-        <v>78344</v>
+        <v>79225</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4075,21 +4066,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4099,10 +4090,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436183</v>
+        <v>436129</v>
       </c>
       <c r="R34" t="n">
-        <v>6738020</v>
+        <v>6737975</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,10 +4152,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347961</v>
+        <v>121347170</v>
       </c>
       <c r="B35" t="n">
-        <v>100364</v>
+        <v>78607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4173,38 +4164,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435592</v>
+        <v>436138</v>
       </c>
       <c r="R35" t="n">
-        <v>6737627</v>
+        <v>6737980</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4263,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346658</v>
+        <v>121346680</v>
       </c>
       <c r="B36" t="n">
-        <v>74652</v>
+        <v>78343</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4275,25 +4266,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4303,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436188</v>
+        <v>436183</v>
       </c>
       <c r="R36" t="n">
-        <v>6738012</v>
+        <v>6738020</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4365,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346697</v>
+        <v>121346569</v>
       </c>
       <c r="B37" t="n">
-        <v>74652</v>
+        <v>78607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4377,25 +4368,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4405,10 +4396,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436180</v>
+        <v>436212</v>
       </c>
       <c r="R37" t="n">
-        <v>6737996</v>
+        <v>6737992</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,10 +4458,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347759</v>
+        <v>121347381</v>
       </c>
       <c r="B38" t="n">
-        <v>78607</v>
+        <v>78641</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4483,21 +4474,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4507,10 +4498,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435691</v>
+        <v>435997</v>
       </c>
       <c r="R38" t="n">
-        <v>6737739</v>
+        <v>6737899</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,7 +4560,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121347925</v>
+        <v>121347826</v>
       </c>
       <c r="B39" t="n">
         <v>98098</v>
@@ -4604,7 +4595,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4618,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435579</v>
+        <v>435632</v>
       </c>
       <c r="R39" t="n">
-        <v>6737662</v>
+        <v>6737702</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121346617</v>
+        <v>121347925</v>
       </c>
       <c r="B40" t="n">
-        <v>79225</v>
+        <v>98098</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4692,38 +4683,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436197</v>
+        <v>435579</v>
       </c>
       <c r="R40" t="n">
-        <v>6737992</v>
+        <v>6737662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374888</v>
+        <v>121374883</v>
       </c>
       <c r="B41" t="n">
-        <v>91396</v>
+        <v>91646</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435889</v>
+        <v>435879</v>
       </c>
       <c r="R41" t="n">
-        <v>6737827</v>
+        <v>6737803</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374881</v>
+        <v>121374889</v>
       </c>
       <c r="B42" t="n">
-        <v>92020</v>
+        <v>92001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435851</v>
+        <v>435889</v>
       </c>
       <c r="R42" t="n">
-        <v>6737817</v>
+        <v>6737819</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,10 +4986,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374892</v>
+        <v>121374881</v>
       </c>
       <c r="B43" t="n">
-        <v>95392</v>
+        <v>92020</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,25 +4998,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>1968</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5026,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435973</v>
+        <v>435851</v>
       </c>
       <c r="R43" t="n">
-        <v>6737875</v>
+        <v>6737817</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374899</v>
+        <v>121374882</v>
       </c>
       <c r="B44" t="n">
-        <v>91997</v>
+        <v>90727</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,25 +5100,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2058</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436217</v>
+        <v>435870</v>
       </c>
       <c r="R44" t="n">
-        <v>6737988</v>
+        <v>6737805</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374886</v>
+        <v>121374899</v>
       </c>
       <c r="B45" t="n">
-        <v>91991</v>
+        <v>91997</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,25 +5202,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>788</v>
+        <v>2058</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435868</v>
+        <v>436217</v>
       </c>
       <c r="R45" t="n">
-        <v>6737835</v>
+        <v>6737988</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374885</v>
+        <v>121374891</v>
       </c>
       <c r="B46" t="n">
-        <v>98434</v>
+        <v>100273</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219880</v>
+        <v>222771</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435878</v>
+        <v>435907</v>
       </c>
       <c r="R46" t="n">
-        <v>6737810</v>
+        <v>6737812</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5376,6 +5376,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5394,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374889</v>
+        <v>121374885</v>
       </c>
       <c r="B47" t="n">
-        <v>92001</v>
+        <v>98434</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5410,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>219880</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5434,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435889</v>
+        <v>435878</v>
       </c>
       <c r="R47" t="n">
-        <v>6737819</v>
+        <v>6737810</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5496,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374882</v>
+        <v>121374879</v>
       </c>
       <c r="B48" t="n">
-        <v>90727</v>
+        <v>91646</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5508,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5536,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435870</v>
+        <v>435838</v>
       </c>
       <c r="R48" t="n">
-        <v>6737805</v>
+        <v>6737809</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5598,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374891</v>
+        <v>121374888</v>
       </c>
       <c r="B49" t="n">
-        <v>100273</v>
+        <v>91396</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5614,21 +5615,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222771</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5638,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435907</v>
+        <v>435889</v>
       </c>
       <c r="R49" t="n">
-        <v>6737812</v>
+        <v>6737827</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5682,7 +5683,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374883</v>
+        <v>121374886</v>
       </c>
       <c r="B50" t="n">
-        <v>91646</v>
+        <v>91991</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435879</v>
+        <v>435868</v>
       </c>
       <c r="R50" t="n">
-        <v>6737803</v>
+        <v>6737835</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374879</v>
+        <v>121374892</v>
       </c>
       <c r="B51" t="n">
-        <v>91646</v>
+        <v>95392</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435838</v>
+        <v>435973</v>
       </c>
       <c r="R51" t="n">
-        <v>6737809</v>
+        <v>6737875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347759</v>
+        <v>121347838</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>91153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,25 +1161,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435691</v>
+        <v>435602</v>
       </c>
       <c r="R6" t="n">
-        <v>6737739</v>
+        <v>6737684</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347838</v>
+        <v>121347759</v>
       </c>
       <c r="B7" t="n">
-        <v>91153</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435602</v>
+        <v>435691</v>
       </c>
       <c r="R7" t="n">
-        <v>6737684</v>
+        <v>6737739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347275</v>
+        <v>121347401</v>
       </c>
       <c r="B14" t="n">
-        <v>98098</v>
+        <v>95392</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,47 +1986,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436019</v>
+        <v>435964</v>
       </c>
       <c r="R14" t="n">
-        <v>6737925</v>
+        <v>6737892</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347953</v>
+        <v>121347275</v>
       </c>
       <c r="B15" t="n">
-        <v>100364</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,38 +2088,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435579</v>
+        <v>436019</v>
       </c>
       <c r="R15" t="n">
-        <v>6737637</v>
+        <v>6737925</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346617</v>
+        <v>121347953</v>
       </c>
       <c r="B16" t="n">
-        <v>79225</v>
+        <v>100364</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,38 +2199,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436197</v>
+        <v>435579</v>
       </c>
       <c r="R16" t="n">
-        <v>6737992</v>
+        <v>6737637</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347401</v>
+        <v>121346617</v>
       </c>
       <c r="B17" t="n">
-        <v>95392</v>
+        <v>79225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,38 +2301,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435964</v>
+        <v>436197</v>
       </c>
       <c r="R17" t="n">
-        <v>6737892</v>
+        <v>6737992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374888</v>
+        <v>121374886</v>
       </c>
       <c r="B49" t="n">
-        <v>91396</v>
+        <v>91991</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,25 +5611,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435889</v>
+        <v>435868</v>
       </c>
       <c r="R49" t="n">
-        <v>6737827</v>
+        <v>6737835</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374886</v>
+        <v>121374888</v>
       </c>
       <c r="B50" t="n">
-        <v>91991</v>
+        <v>91396</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>788</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435868</v>
+        <v>435889</v>
       </c>
       <c r="R50" t="n">
-        <v>6737835</v>
+        <v>6737827</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>121347743</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347503</v>
+        <v>121347858</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>100370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,47 +1050,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435899</v>
+        <v>435596</v>
       </c>
       <c r="R5" t="n">
-        <v>6737841</v>
+        <v>6737662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347838</v>
+        <v>121346617</v>
       </c>
       <c r="B6" t="n">
-        <v>91153</v>
+        <v>79226</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,38 +1152,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435602</v>
+        <v>436197</v>
       </c>
       <c r="R6" t="n">
-        <v>6737684</v>
+        <v>6737992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347759</v>
+        <v>121346680</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,34 +1258,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435691</v>
+        <v>436183</v>
       </c>
       <c r="R7" t="n">
-        <v>6737739</v>
+        <v>6738020</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121348302</v>
+        <v>121347503</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,38 +1356,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436091</v>
+        <v>435899</v>
       </c>
       <c r="R8" t="n">
-        <v>6737907</v>
+        <v>6737841</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347412</v>
+        <v>121347401</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>95398</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,37 +1467,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
@@ -1566,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347858</v>
+        <v>121347961</v>
       </c>
       <c r="B10" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435596</v>
+        <v>435592</v>
       </c>
       <c r="R10" t="n">
-        <v>6737662</v>
+        <v>6737627</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347142</v>
+        <v>121347836</v>
       </c>
       <c r="B11" t="n">
-        <v>78641</v>
+        <v>90719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,34 +1675,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436148</v>
+        <v>435602</v>
       </c>
       <c r="R11" t="n">
-        <v>6737987</v>
+        <v>6737684</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347961</v>
+        <v>121346697</v>
       </c>
       <c r="B12" t="n">
-        <v>100364</v>
+        <v>74653</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,34 +1777,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435592</v>
+        <v>436180</v>
       </c>
       <c r="R12" t="n">
-        <v>6737627</v>
+        <v>6737996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346735</v>
+        <v>121347216</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>79226</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1879,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436168</v>
+        <v>436129</v>
       </c>
       <c r="R13" t="n">
-        <v>6737999</v>
+        <v>6737975</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347401</v>
+        <v>121348117</v>
       </c>
       <c r="B14" t="n">
-        <v>95392</v>
+        <v>100370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1981,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2005,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435964</v>
+        <v>435853</v>
       </c>
       <c r="R14" t="n">
-        <v>6737892</v>
+        <v>6737770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347275</v>
+        <v>121347759</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,47 +2079,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436019</v>
+        <v>435691</v>
       </c>
       <c r="R15" t="n">
-        <v>6737925</v>
+        <v>6737739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347953</v>
+        <v>121347170</v>
       </c>
       <c r="B16" t="n">
-        <v>100364</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,38 +2181,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435579</v>
+        <v>436138</v>
       </c>
       <c r="R16" t="n">
-        <v>6737637</v>
+        <v>6737980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346617</v>
+        <v>121348251</v>
       </c>
       <c r="B17" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,34 +2287,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436197</v>
+        <v>436011</v>
       </c>
       <c r="R17" t="n">
-        <v>6737992</v>
+        <v>6737862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2373,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121348117</v>
+        <v>121347142</v>
       </c>
       <c r="B18" t="n">
-        <v>100364</v>
+        <v>78642</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,38 +2385,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435853</v>
+        <v>436148</v>
       </c>
       <c r="R18" t="n">
-        <v>6737770</v>
+        <v>6737987</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,10 +2475,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121348177</v>
+        <v>121347850</v>
       </c>
       <c r="B19" t="n">
-        <v>90678</v>
+        <v>94506</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,21 +2491,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2533,10 +2515,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435961</v>
+        <v>435603</v>
       </c>
       <c r="R19" t="n">
-        <v>6737833</v>
+        <v>6737665</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2595,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346787</v>
+        <v>121347412</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,38 +2589,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436175</v>
+        <v>435964</v>
       </c>
       <c r="R20" t="n">
-        <v>6737983</v>
+        <v>6737892</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121348251</v>
+        <v>121347087</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>57508</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2713,34 +2704,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436011</v>
+        <v>436159</v>
       </c>
       <c r="R21" t="n">
-        <v>6737862</v>
+        <v>6737985</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121346881</v>
+        <v>121347826</v>
       </c>
       <c r="B22" t="n">
-        <v>78641</v>
+        <v>98104</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,38 +2811,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436163</v>
+        <v>435632</v>
       </c>
       <c r="R22" t="n">
-        <v>6737990</v>
+        <v>6737702</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347180</v>
+        <v>121346787</v>
       </c>
       <c r="B23" t="n">
-        <v>79225</v>
+        <v>78608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,21 +2926,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436132</v>
+        <v>436175</v>
       </c>
       <c r="R23" t="n">
-        <v>6737977</v>
+        <v>6737983</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347850</v>
+        <v>121347180</v>
       </c>
       <c r="B24" t="n">
-        <v>94500</v>
+        <v>79226</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,38 +3024,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435603</v>
+        <v>436132</v>
       </c>
       <c r="R24" t="n">
-        <v>6737665</v>
+        <v>6737977</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,10 +3114,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346682</v>
+        <v>121347949</v>
       </c>
       <c r="B25" t="n">
-        <v>78344</v>
+        <v>98104</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,38 +3126,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436183</v>
+        <v>435576</v>
       </c>
       <c r="R25" t="n">
-        <v>6738020</v>
+        <v>6737633</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347315</v>
+        <v>121347838</v>
       </c>
       <c r="B26" t="n">
-        <v>80564</v>
+        <v>91159</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,25 +3237,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3247,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436015</v>
+        <v>435602</v>
       </c>
       <c r="R26" t="n">
-        <v>6737908</v>
+        <v>6737684</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3309,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347836</v>
+        <v>121348302</v>
       </c>
       <c r="B27" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3325,34 +3343,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435602</v>
+        <v>436091</v>
       </c>
       <c r="R27" t="n">
-        <v>6737684</v>
+        <v>6737907</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3414,7 +3432,7 @@
         <v>121346658</v>
       </c>
       <c r="B28" t="n">
-        <v>74652</v>
+        <v>74653</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3513,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346697</v>
+        <v>121348177</v>
       </c>
       <c r="B29" t="n">
-        <v>74652</v>
+        <v>90684</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3529,34 +3547,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436180</v>
+        <v>435961</v>
       </c>
       <c r="R29" t="n">
-        <v>6737996</v>
+        <v>6737833</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347949</v>
+        <v>121347381</v>
       </c>
       <c r="B30" t="n">
-        <v>98098</v>
+        <v>78642</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3627,47 +3645,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435576</v>
+        <v>435997</v>
       </c>
       <c r="R30" t="n">
-        <v>6737633</v>
+        <v>6737899</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3726,10 +3735,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121347321</v>
+        <v>121347953</v>
       </c>
       <c r="B31" t="n">
-        <v>90713</v>
+        <v>100370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3738,38 +3747,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436013</v>
+        <v>435579</v>
       </c>
       <c r="R31" t="n">
-        <v>6737929</v>
+        <v>6737637</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,10 +3837,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347087</v>
+        <v>121346682</v>
       </c>
       <c r="B32" t="n">
-        <v>57507</v>
+        <v>78345</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3844,43 +3853,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436159</v>
+        <v>436183</v>
       </c>
       <c r="R32" t="n">
-        <v>6737985</v>
+        <v>6738020</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3939,10 +3939,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121348221</v>
+        <v>121347315</v>
       </c>
       <c r="B33" t="n">
-        <v>98098</v>
+        <v>80565</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3951,47 +3951,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435979</v>
+        <v>436015</v>
       </c>
       <c r="R33" t="n">
-        <v>6737851</v>
+        <v>6737908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4050,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347216</v>
+        <v>121347321</v>
       </c>
       <c r="B34" t="n">
-        <v>79225</v>
+        <v>90719</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4066,21 +4057,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4090,10 +4081,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436129</v>
+        <v>436013</v>
       </c>
       <c r="R34" t="n">
-        <v>6737975</v>
+        <v>6737929</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4152,10 +4143,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347170</v>
+        <v>121348221</v>
       </c>
       <c r="B35" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,38 +4155,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436138</v>
+        <v>435979</v>
       </c>
       <c r="R35" t="n">
-        <v>6737980</v>
+        <v>6737851</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346680</v>
+        <v>121346881</v>
       </c>
       <c r="B36" t="n">
-        <v>78343</v>
+        <v>78642</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436183</v>
+        <v>436163</v>
       </c>
       <c r="R36" t="n">
-        <v>6738020</v>
+        <v>6737990</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346569</v>
+        <v>121347925</v>
       </c>
       <c r="B37" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,38 +4368,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436212</v>
+        <v>435579</v>
       </c>
       <c r="R37" t="n">
-        <v>6737992</v>
+        <v>6737662</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,10 +4467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347381</v>
+        <v>121346735</v>
       </c>
       <c r="B38" t="n">
-        <v>78641</v>
+        <v>78608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4474,34 +4483,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435997</v>
+        <v>436168</v>
       </c>
       <c r="R38" t="n">
-        <v>6737899</v>
+        <v>6737999</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4560,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121347826</v>
+        <v>121346569</v>
       </c>
       <c r="B39" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4572,47 +4581,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435632</v>
+        <v>436212</v>
       </c>
       <c r="R39" t="n">
-        <v>6737702</v>
+        <v>6737992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121347925</v>
+        <v>121347275</v>
       </c>
       <c r="B40" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4716,14 +4716,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435579</v>
+        <v>436019</v>
       </c>
       <c r="R40" t="n">
-        <v>6737662</v>
+        <v>6737925</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374883</v>
+        <v>121374879</v>
       </c>
       <c r="B41" t="n">
-        <v>91646</v>
+        <v>91652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435879</v>
+        <v>435838</v>
       </c>
       <c r="R41" t="n">
-        <v>6737803</v>
+        <v>6737809</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374889</v>
+        <v>121374892</v>
       </c>
       <c r="B42" t="n">
-        <v>92001</v>
+        <v>95398</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435889</v>
+        <v>435973</v>
       </c>
       <c r="R42" t="n">
-        <v>6737819</v>
+        <v>6737875</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,7 +4989,7 @@
         <v>121374881</v>
       </c>
       <c r="B43" t="n">
-        <v>92020</v>
+        <v>92026</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374882</v>
+        <v>121374899</v>
       </c>
       <c r="B44" t="n">
-        <v>90727</v>
+        <v>92003</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,25 +5100,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>2058</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435870</v>
+        <v>436217</v>
       </c>
       <c r="R44" t="n">
-        <v>6737805</v>
+        <v>6737988</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5190,10 +5190,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374899</v>
+        <v>121374883</v>
       </c>
       <c r="B45" t="n">
-        <v>91997</v>
+        <v>91652</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5202,25 +5202,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2058</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5230,10 +5230,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436217</v>
+        <v>435879</v>
       </c>
       <c r="R45" t="n">
-        <v>6737988</v>
+        <v>6737803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374891</v>
+        <v>121374885</v>
       </c>
       <c r="B46" t="n">
-        <v>100273</v>
+        <v>98440</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5308,21 +5308,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222771</v>
+        <v>219880</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435907</v>
+        <v>435878</v>
       </c>
       <c r="R46" t="n">
-        <v>6737812</v>
+        <v>6737810</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5376,7 +5376,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5395,10 +5394,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374885</v>
+        <v>121374891</v>
       </c>
       <c r="B47" t="n">
-        <v>98434</v>
+        <v>100279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5410,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219880</v>
+        <v>222771</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5434,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435878</v>
+        <v>435907</v>
       </c>
       <c r="R47" t="n">
-        <v>6737810</v>
+        <v>6737812</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5479,6 +5478,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374879</v>
+        <v>121374889</v>
       </c>
       <c r="B48" t="n">
-        <v>91646</v>
+        <v>92007</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,21 +5513,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435838</v>
+        <v>435889</v>
       </c>
       <c r="R48" t="n">
-        <v>6737809</v>
+        <v>6737819</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5602,7 +5602,7 @@
         <v>121374886</v>
       </c>
       <c r="B49" t="n">
-        <v>91991</v>
+        <v>91997</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374888</v>
+        <v>121374882</v>
       </c>
       <c r="B50" t="n">
-        <v>91396</v>
+        <v>90733</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435889</v>
+        <v>435870</v>
       </c>
       <c r="R50" t="n">
-        <v>6737827</v>
+        <v>6737805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374892</v>
+        <v>121374888</v>
       </c>
       <c r="B51" t="n">
-        <v>95392</v>
+        <v>91402</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>3298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435973</v>
+        <v>435889</v>
       </c>
       <c r="R51" t="n">
-        <v>6737875</v>
+        <v>6737827</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347743</v>
+        <v>121347170</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,47 +939,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435764</v>
+        <v>436138</v>
       </c>
       <c r="R4" t="n">
-        <v>6737744</v>
+        <v>6737980</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347858</v>
+        <v>121347925</v>
       </c>
       <c r="B5" t="n">
-        <v>100370</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,35 +1041,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435596</v>
+        <v>435579</v>
       </c>
       <c r="R5" t="n">
         <v>6737662</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346617</v>
+        <v>121348117</v>
       </c>
       <c r="B6" t="n">
-        <v>79226</v>
+        <v>100371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1152,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436197</v>
+        <v>435853</v>
       </c>
       <c r="R6" t="n">
-        <v>6737992</v>
+        <v>6737770</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1245,7 +1245,7 @@
         <v>121346680</v>
       </c>
       <c r="B7" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347503</v>
+        <v>121347836</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,47 +1356,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435899</v>
+        <v>435602</v>
       </c>
       <c r="R8" t="n">
-        <v>6737841</v>
+        <v>6737684</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347401</v>
+        <v>121346735</v>
       </c>
       <c r="B9" t="n">
-        <v>95398</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,38 +1458,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435964</v>
+        <v>436168</v>
       </c>
       <c r="R9" t="n">
-        <v>6737892</v>
+        <v>6737999</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347961</v>
+        <v>121346881</v>
       </c>
       <c r="B10" t="n">
-        <v>100370</v>
+        <v>78643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,38 +1560,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435592</v>
+        <v>436163</v>
       </c>
       <c r="R10" t="n">
-        <v>6737627</v>
+        <v>6737990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347836</v>
+        <v>121347315</v>
       </c>
       <c r="B11" t="n">
-        <v>90719</v>
+        <v>80566</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,21 +1666,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1699,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435602</v>
+        <v>436015</v>
       </c>
       <c r="R11" t="n">
-        <v>6737684</v>
+        <v>6737908</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346697</v>
+        <v>121347401</v>
       </c>
       <c r="B12" t="n">
-        <v>74653</v>
+        <v>95399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,34 +1768,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436180</v>
+        <v>435964</v>
       </c>
       <c r="R12" t="n">
-        <v>6737996</v>
+        <v>6737892</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,10 +1854,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347216</v>
+        <v>121347826</v>
       </c>
       <c r="B13" t="n">
-        <v>79226</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,38 +1866,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436129</v>
+        <v>435632</v>
       </c>
       <c r="R13" t="n">
-        <v>6737975</v>
+        <v>6737702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121348117</v>
+        <v>121346682</v>
       </c>
       <c r="B14" t="n">
-        <v>100370</v>
+        <v>78346</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,38 +1977,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435853</v>
+        <v>436183</v>
       </c>
       <c r="R14" t="n">
-        <v>6737770</v>
+        <v>6738020</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347759</v>
+        <v>121347087</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,34 +2083,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435691</v>
+        <v>436159</v>
       </c>
       <c r="R15" t="n">
-        <v>6737739</v>
+        <v>6737985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347170</v>
+        <v>121348251</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,14 +2214,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436138</v>
+        <v>436011</v>
       </c>
       <c r="R16" t="n">
-        <v>6737980</v>
+        <v>6737862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121348251</v>
+        <v>121347961</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
+        <v>100371</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2283,25 +2292,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2311,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436011</v>
+        <v>435592</v>
       </c>
       <c r="R17" t="n">
-        <v>6737862</v>
+        <v>6737627</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347142</v>
+        <v>121346569</v>
       </c>
       <c r="B18" t="n">
-        <v>78642</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2389,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2413,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436148</v>
+        <v>436212</v>
       </c>
       <c r="R18" t="n">
-        <v>6737987</v>
+        <v>6737992</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347850</v>
+        <v>121346658</v>
       </c>
       <c r="B19" t="n">
-        <v>94506</v>
+        <v>74654</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2491,34 +2500,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2809</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435603</v>
+        <v>436188</v>
       </c>
       <c r="R19" t="n">
-        <v>6737665</v>
+        <v>6738012</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347412</v>
+        <v>121347743</v>
       </c>
       <c r="B20" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2612,7 +2621,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2626,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435964</v>
+        <v>435764</v>
       </c>
       <c r="R20" t="n">
-        <v>6737892</v>
+        <v>6737744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347087</v>
+        <v>121347850</v>
       </c>
       <c r="B21" t="n">
-        <v>57508</v>
+        <v>94507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2700,47 +2709,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436159</v>
+        <v>435603</v>
       </c>
       <c r="R21" t="n">
-        <v>6737985</v>
+        <v>6737665</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347826</v>
+        <v>121347216</v>
       </c>
       <c r="B22" t="n">
-        <v>98104</v>
+        <v>79227</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,47 +2811,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435632</v>
+        <v>436129</v>
       </c>
       <c r="R22" t="n">
-        <v>6737702</v>
+        <v>6737975</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346787</v>
+        <v>121347838</v>
       </c>
       <c r="B23" t="n">
-        <v>78608</v>
+        <v>91160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,38 +2913,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436175</v>
+        <v>435602</v>
       </c>
       <c r="R23" t="n">
-        <v>6737983</v>
+        <v>6737684</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,10 +3003,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347180</v>
+        <v>121348221</v>
       </c>
       <c r="B24" t="n">
-        <v>79226</v>
+        <v>98105</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,38 +3015,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436132</v>
+        <v>435979</v>
       </c>
       <c r="R24" t="n">
-        <v>6737977</v>
+        <v>6737851</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347949</v>
+        <v>121347759</v>
       </c>
       <c r="B25" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3126,47 +3126,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435576</v>
+        <v>435691</v>
       </c>
       <c r="R25" t="n">
-        <v>6737633</v>
+        <v>6737739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347838</v>
+        <v>121346697</v>
       </c>
       <c r="B26" t="n">
-        <v>91159</v>
+        <v>74654</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,38 +3228,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435602</v>
+        <v>436180</v>
       </c>
       <c r="R26" t="n">
-        <v>6737684</v>
+        <v>6737996</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121348302</v>
+        <v>121348177</v>
       </c>
       <c r="B27" t="n">
-        <v>78608</v>
+        <v>90685</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,38 +3330,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436091</v>
+        <v>435961</v>
       </c>
       <c r="R27" t="n">
-        <v>6737907</v>
+        <v>6737833</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3420,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346658</v>
+        <v>121347503</v>
       </c>
       <c r="B28" t="n">
-        <v>74653</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,38 +3432,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436188</v>
+        <v>435899</v>
       </c>
       <c r="R28" t="n">
-        <v>6738012</v>
+        <v>6737841</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121348177</v>
+        <v>121347275</v>
       </c>
       <c r="B29" t="n">
-        <v>90684</v>
+        <v>98105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3543,38 +3543,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435961</v>
+        <v>436019</v>
       </c>
       <c r="R29" t="n">
-        <v>6737833</v>
+        <v>6737925</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347381</v>
+        <v>121348302</v>
       </c>
       <c r="B30" t="n">
-        <v>78642</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3649,34 +3658,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435997</v>
+        <v>436091</v>
       </c>
       <c r="R30" t="n">
-        <v>6737899</v>
+        <v>6737907</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121347953</v>
+        <v>121346617</v>
       </c>
       <c r="B31" t="n">
-        <v>100370</v>
+        <v>79227</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3747,38 +3756,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435579</v>
+        <v>436197</v>
       </c>
       <c r="R31" t="n">
-        <v>6737637</v>
+        <v>6737992</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121346682</v>
+        <v>121347412</v>
       </c>
       <c r="B32" t="n">
-        <v>78345</v>
+        <v>98105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,38 +3858,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436183</v>
+        <v>435964</v>
       </c>
       <c r="R32" t="n">
-        <v>6738020</v>
+        <v>6737892</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3939,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121347315</v>
+        <v>121347381</v>
       </c>
       <c r="B33" t="n">
-        <v>80565</v>
+        <v>78643</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3955,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3979,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436015</v>
+        <v>435997</v>
       </c>
       <c r="R33" t="n">
-        <v>6737908</v>
+        <v>6737899</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4041,10 +4059,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347321</v>
+        <v>121346787</v>
       </c>
       <c r="B34" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4057,21 +4075,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4081,10 +4099,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436013</v>
+        <v>436175</v>
       </c>
       <c r="R34" t="n">
-        <v>6737929</v>
+        <v>6737983</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4143,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121348221</v>
+        <v>121347858</v>
       </c>
       <c r="B35" t="n">
-        <v>98104</v>
+        <v>100371</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4155,47 +4173,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435979</v>
+        <v>435596</v>
       </c>
       <c r="R35" t="n">
-        <v>6737851</v>
+        <v>6737662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,10 +4263,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346881</v>
+        <v>121347949</v>
       </c>
       <c r="B36" t="n">
-        <v>78642</v>
+        <v>98105</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,38 +4275,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436163</v>
+        <v>435576</v>
       </c>
       <c r="R36" t="n">
-        <v>6737990</v>
+        <v>6737633</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347925</v>
+        <v>121347180</v>
       </c>
       <c r="B37" t="n">
-        <v>98104</v>
+        <v>79227</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,47 +4386,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435579</v>
+        <v>436132</v>
       </c>
       <c r="R37" t="n">
-        <v>6737662</v>
+        <v>6737977</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121346735</v>
+        <v>121347142</v>
       </c>
       <c r="B38" t="n">
-        <v>78608</v>
+        <v>78643</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4483,21 +4492,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4507,10 +4516,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436168</v>
+        <v>436148</v>
       </c>
       <c r="R38" t="n">
-        <v>6737999</v>
+        <v>6737987</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4569,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346569</v>
+        <v>121347321</v>
       </c>
       <c r="B39" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4585,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4609,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436212</v>
+        <v>436013</v>
       </c>
       <c r="R39" t="n">
-        <v>6737992</v>
+        <v>6737929</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121347275</v>
+        <v>121347953</v>
       </c>
       <c r="B40" t="n">
-        <v>98104</v>
+        <v>100371</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4683,47 +4692,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436019</v>
+        <v>435579</v>
       </c>
       <c r="R40" t="n">
-        <v>6737925</v>
+        <v>6737637</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374879</v>
+        <v>121374889</v>
       </c>
       <c r="B41" t="n">
-        <v>91652</v>
+        <v>92008</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435838</v>
+        <v>435889</v>
       </c>
       <c r="R41" t="n">
-        <v>6737809</v>
+        <v>6737819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374892</v>
+        <v>121374891</v>
       </c>
       <c r="B42" t="n">
-        <v>95398</v>
+        <v>100280</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435973</v>
+        <v>435907</v>
       </c>
       <c r="R42" t="n">
-        <v>6737875</v>
+        <v>6737812</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4968,6 +4968,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4986,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374881</v>
+        <v>121374888</v>
       </c>
       <c r="B43" t="n">
-        <v>92026</v>
+        <v>91403</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,25 +4999,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1968</v>
+        <v>3298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435851</v>
+        <v>435889</v>
       </c>
       <c r="R43" t="n">
-        <v>6737817</v>
+        <v>6737827</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5088,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374899</v>
+        <v>121374885</v>
       </c>
       <c r="B44" t="n">
-        <v>92003</v>
+        <v>98441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,25 +5101,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2058</v>
+        <v>219880</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5128,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436217</v>
+        <v>435878</v>
       </c>
       <c r="R44" t="n">
-        <v>6737988</v>
+        <v>6737810</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5193,7 +5194,7 @@
         <v>121374883</v>
       </c>
       <c r="B45" t="n">
-        <v>91652</v>
+        <v>91653</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5292,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374885</v>
+        <v>121374886</v>
       </c>
       <c r="B46" t="n">
-        <v>98440</v>
+        <v>91998</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5304,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219880</v>
+        <v>788</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5332,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435878</v>
+        <v>435868</v>
       </c>
       <c r="R46" t="n">
-        <v>6737810</v>
+        <v>6737835</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5394,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374891</v>
+        <v>121374879</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>91653</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5410,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5434,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435907</v>
+        <v>435838</v>
       </c>
       <c r="R47" t="n">
-        <v>6737812</v>
+        <v>6737809</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5478,7 +5479,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374889</v>
+        <v>121374899</v>
       </c>
       <c r="B48" t="n">
-        <v>92007</v>
+        <v>92004</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>2058</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435889</v>
+        <v>436217</v>
       </c>
       <c r="R48" t="n">
-        <v>6737819</v>
+        <v>6737988</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374886</v>
+        <v>121374892</v>
       </c>
       <c r="B49" t="n">
-        <v>91997</v>
+        <v>95399</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,25 +5611,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435868</v>
+        <v>435973</v>
       </c>
       <c r="R49" t="n">
-        <v>6737835</v>
+        <v>6737875</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374882</v>
+        <v>121374881</v>
       </c>
       <c r="B50" t="n">
-        <v>90733</v>
+        <v>92027</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5717,21 +5717,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>1968</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435870</v>
+        <v>435851</v>
       </c>
       <c r="R50" t="n">
-        <v>6737805</v>
+        <v>6737817</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374888</v>
+        <v>121374882</v>
       </c>
       <c r="B51" t="n">
-        <v>91402</v>
+        <v>90734</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5815,25 +5815,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435889</v>
+        <v>435870</v>
       </c>
       <c r="R51" t="n">
-        <v>6737827</v>
+        <v>6737805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347170</v>
+        <v>121347836</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,34 +943,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436138</v>
+        <v>435602</v>
       </c>
       <c r="R4" t="n">
-        <v>6737980</v>
+        <v>6737684</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347925</v>
+        <v>121348221</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435579</v>
+        <v>435979</v>
       </c>
       <c r="R5" t="n">
-        <v>6737662</v>
+        <v>6737851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121348117</v>
+        <v>121347401</v>
       </c>
       <c r="B6" t="n">
-        <v>100371</v>
+        <v>95399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435853</v>
+        <v>435964</v>
       </c>
       <c r="R6" t="n">
-        <v>6737770</v>
+        <v>6737892</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346680</v>
+        <v>121347412</v>
       </c>
       <c r="B7" t="n">
-        <v>78345</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1254,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436183</v>
+        <v>435964</v>
       </c>
       <c r="R7" t="n">
-        <v>6738020</v>
+        <v>6737892</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347836</v>
+        <v>121347216</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>79227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,34 +1369,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435602</v>
+        <v>436129</v>
       </c>
       <c r="R8" t="n">
-        <v>6737684</v>
+        <v>6737975</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346735</v>
+        <v>121346680</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1486,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436168</v>
+        <v>436183</v>
       </c>
       <c r="R9" t="n">
-        <v>6737999</v>
+        <v>6738020</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346881</v>
+        <v>121347949</v>
       </c>
       <c r="B10" t="n">
-        <v>78643</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,38 +1569,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436163</v>
+        <v>435576</v>
       </c>
       <c r="R10" t="n">
-        <v>6737990</v>
+        <v>6737633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347315</v>
+        <v>121348117</v>
       </c>
       <c r="B11" t="n">
-        <v>80566</v>
+        <v>100371</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,25 +1680,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1690,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436015</v>
+        <v>435853</v>
       </c>
       <c r="R11" t="n">
-        <v>6737908</v>
+        <v>6737770</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347401</v>
+        <v>121347087</v>
       </c>
       <c r="B12" t="n">
-        <v>95399</v>
+        <v>57509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,38 +1782,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>435964</v>
+        <v>436159</v>
       </c>
       <c r="R12" t="n">
-        <v>6737892</v>
+        <v>6737985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347826</v>
+        <v>121348251</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,47 +1893,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435632</v>
+        <v>436011</v>
       </c>
       <c r="R13" t="n">
-        <v>6737702</v>
+        <v>6737862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346682</v>
+        <v>121347180</v>
       </c>
       <c r="B14" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2005,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436183</v>
+        <v>436132</v>
       </c>
       <c r="R14" t="n">
-        <v>6738020</v>
+        <v>6737977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347087</v>
+        <v>121348177</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>90685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,47 +2097,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436159</v>
+        <v>435961</v>
       </c>
       <c r="R15" t="n">
-        <v>6737985</v>
+        <v>6737833</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121348251</v>
+        <v>121347759</v>
       </c>
       <c r="B16" t="n">
         <v>78609</v>
@@ -2218,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436011</v>
+        <v>435691</v>
       </c>
       <c r="R16" t="n">
-        <v>6737862</v>
+        <v>6737739</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347961</v>
+        <v>121348302</v>
       </c>
       <c r="B17" t="n">
-        <v>100371</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,38 +2301,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435592</v>
+        <v>436091</v>
       </c>
       <c r="R17" t="n">
-        <v>6737627</v>
+        <v>6737907</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346569</v>
+        <v>121347858</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>100371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,38 +2403,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436212</v>
+        <v>435596</v>
       </c>
       <c r="R18" t="n">
-        <v>6737992</v>
+        <v>6737662</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346658</v>
+        <v>121347925</v>
       </c>
       <c r="B19" t="n">
-        <v>74654</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2496,38 +2505,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436188</v>
+        <v>435579</v>
       </c>
       <c r="R19" t="n">
-        <v>6738012</v>
+        <v>6737662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347743</v>
+        <v>121347953</v>
       </c>
       <c r="B20" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2598,47 +2616,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435764</v>
+        <v>435579</v>
       </c>
       <c r="R20" t="n">
-        <v>6737744</v>
+        <v>6737637</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347850</v>
+        <v>121347170</v>
       </c>
       <c r="B21" t="n">
-        <v>94507</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2709,38 +2718,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435603</v>
+        <v>436138</v>
       </c>
       <c r="R21" t="n">
-        <v>6737665</v>
+        <v>6737980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,10 +2808,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347216</v>
+        <v>121347826</v>
       </c>
       <c r="B22" t="n">
-        <v>79227</v>
+        <v>98105</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,38 +2820,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436129</v>
+        <v>435632</v>
       </c>
       <c r="R22" t="n">
-        <v>6737975</v>
+        <v>6737702</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2919,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347838</v>
+        <v>121346735</v>
       </c>
       <c r="B23" t="n">
-        <v>91160</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,38 +2931,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435602</v>
+        <v>436168</v>
       </c>
       <c r="R23" t="n">
-        <v>6737684</v>
+        <v>6737999</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121348221</v>
+        <v>121346697</v>
       </c>
       <c r="B24" t="n">
-        <v>98105</v>
+        <v>74654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,47 +3033,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>435979</v>
+        <v>436180</v>
       </c>
       <c r="R24" t="n">
-        <v>6737851</v>
+        <v>6737996</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3114,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347759</v>
+        <v>121347321</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,34 +3139,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435691</v>
+        <v>436013</v>
       </c>
       <c r="R25" t="n">
-        <v>6737739</v>
+        <v>6737929</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346697</v>
+        <v>121347743</v>
       </c>
       <c r="B26" t="n">
-        <v>74654</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3228,38 +3237,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436180</v>
+        <v>435764</v>
       </c>
       <c r="R26" t="n">
-        <v>6737996</v>
+        <v>6737744</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121348177</v>
+        <v>121346569</v>
       </c>
       <c r="B27" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3330,38 +3348,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435961</v>
+        <v>436212</v>
       </c>
       <c r="R27" t="n">
-        <v>6737833</v>
+        <v>6737992</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3438,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347503</v>
+        <v>121347275</v>
       </c>
       <c r="B28" t="n">
         <v>98105</v>
@@ -3455,7 +3473,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3465,14 +3483,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435899</v>
+        <v>436019</v>
       </c>
       <c r="R28" t="n">
-        <v>6737841</v>
+        <v>6737925</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3531,7 +3549,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347275</v>
+        <v>121347503</v>
       </c>
       <c r="B29" t="n">
         <v>98105</v>
@@ -3566,7 +3584,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3576,14 +3594,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436019</v>
+        <v>435899</v>
       </c>
       <c r="R29" t="n">
-        <v>6737925</v>
+        <v>6737841</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,10 +3660,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121348302</v>
+        <v>121346658</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>74654</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,25 +3672,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,10 +3700,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436091</v>
+        <v>436188</v>
       </c>
       <c r="R30" t="n">
-        <v>6737907</v>
+        <v>6738012</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3744,10 +3762,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346617</v>
+        <v>121346682</v>
       </c>
       <c r="B31" t="n">
-        <v>79227</v>
+        <v>78346</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3760,21 +3778,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436197</v>
+        <v>436183</v>
       </c>
       <c r="R31" t="n">
-        <v>6737992</v>
+        <v>6738020</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,10 +3864,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347412</v>
+        <v>121347381</v>
       </c>
       <c r="B32" t="n">
-        <v>98105</v>
+        <v>78643</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,47 +3876,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435964</v>
+        <v>435997</v>
       </c>
       <c r="R32" t="n">
-        <v>6737892</v>
+        <v>6737899</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,7 +3966,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121347381</v>
+        <v>121346881</v>
       </c>
       <c r="B33" t="n">
         <v>78643</v>
@@ -3993,14 +4002,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>435997</v>
+        <v>436163</v>
       </c>
       <c r="R33" t="n">
-        <v>6737899</v>
+        <v>6737990</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,10 +4068,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121346787</v>
+        <v>121347142</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4075,21 +4084,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4099,10 +4108,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436175</v>
+        <v>436148</v>
       </c>
       <c r="R34" t="n">
-        <v>6737983</v>
+        <v>6737987</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4161,10 +4170,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347858</v>
+        <v>121347315</v>
       </c>
       <c r="B35" t="n">
-        <v>100371</v>
+        <v>80566</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4173,25 +4182,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4201,10 +4210,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435596</v>
+        <v>436015</v>
       </c>
       <c r="R35" t="n">
-        <v>6737662</v>
+        <v>6737908</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4263,10 +4272,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121347949</v>
+        <v>121346787</v>
       </c>
       <c r="B36" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4275,47 +4284,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435576</v>
+        <v>436175</v>
       </c>
       <c r="R36" t="n">
-        <v>6737633</v>
+        <v>6737983</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347180</v>
+        <v>121347961</v>
       </c>
       <c r="B37" t="n">
-        <v>79227</v>
+        <v>100371</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4386,38 +4386,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436132</v>
+        <v>435592</v>
       </c>
       <c r="R37" t="n">
-        <v>6737977</v>
+        <v>6737627</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347142</v>
+        <v>121347838</v>
       </c>
       <c r="B38" t="n">
-        <v>78643</v>
+        <v>91160</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4488,38 +4488,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436148</v>
+        <v>435602</v>
       </c>
       <c r="R38" t="n">
-        <v>6737987</v>
+        <v>6737684</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121347321</v>
+        <v>121346617</v>
       </c>
       <c r="B39" t="n">
-        <v>90720</v>
+        <v>79227</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436013</v>
+        <v>436197</v>
       </c>
       <c r="R39" t="n">
-        <v>6737929</v>
+        <v>6737992</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121347953</v>
+        <v>121347850</v>
       </c>
       <c r="B40" t="n">
-        <v>100371</v>
+        <v>94507</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4696,21 +4696,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>2809</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435579</v>
+        <v>435603</v>
       </c>
       <c r="R40" t="n">
-        <v>6737637</v>
+        <v>6737665</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374889</v>
+        <v>121374881</v>
       </c>
       <c r="B41" t="n">
-        <v>92008</v>
+        <v>92027</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>1968</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435889</v>
+        <v>435851</v>
       </c>
       <c r="R41" t="n">
-        <v>6737819</v>
+        <v>6737817</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374891</v>
+        <v>121374899</v>
       </c>
       <c r="B42" t="n">
-        <v>100280</v>
+        <v>92004</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>2058</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435907</v>
+        <v>436217</v>
       </c>
       <c r="R42" t="n">
-        <v>6737812</v>
+        <v>6737988</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4968,7 +4968,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4987,10 +4986,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374888</v>
+        <v>121374891</v>
       </c>
       <c r="B43" t="n">
-        <v>91403</v>
+        <v>100280</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5003,21 +5002,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3298</v>
+        <v>222771</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435889</v>
+        <v>435907</v>
       </c>
       <c r="R43" t="n">
-        <v>6737827</v>
+        <v>6737812</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5071,6 +5070,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374885</v>
+        <v>121374889</v>
       </c>
       <c r="B44" t="n">
-        <v>98441</v>
+        <v>92008</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5105,21 +5105,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219880</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435878</v>
+        <v>435889</v>
       </c>
       <c r="R44" t="n">
-        <v>6737810</v>
+        <v>6737819</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374883</v>
+        <v>121374886</v>
       </c>
       <c r="B45" t="n">
-        <v>91653</v>
+        <v>91998</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,25 +5203,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435879</v>
+        <v>435868</v>
       </c>
       <c r="R45" t="n">
-        <v>6737803</v>
+        <v>6737835</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374886</v>
+        <v>121374885</v>
       </c>
       <c r="B46" t="n">
-        <v>91998</v>
+        <v>98441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>788</v>
+        <v>219880</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435868</v>
+        <v>435878</v>
       </c>
       <c r="R46" t="n">
-        <v>6737835</v>
+        <v>6737810</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374879</v>
+        <v>121374888</v>
       </c>
       <c r="B47" t="n">
-        <v>91653</v>
+        <v>91403</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435838</v>
+        <v>435889</v>
       </c>
       <c r="R47" t="n">
-        <v>6737809</v>
+        <v>6737827</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374899</v>
+        <v>121374882</v>
       </c>
       <c r="B48" t="n">
-        <v>92004</v>
+        <v>90734</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2058</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436217</v>
+        <v>435870</v>
       </c>
       <c r="R48" t="n">
-        <v>6737988</v>
+        <v>6737805</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374892</v>
+        <v>121374883</v>
       </c>
       <c r="B49" t="n">
-        <v>95399</v>
+        <v>91653</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435973</v>
+        <v>435879</v>
       </c>
       <c r="R49" t="n">
-        <v>6737875</v>
+        <v>6737803</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374881</v>
+        <v>121374892</v>
       </c>
       <c r="B50" t="n">
-        <v>92027</v>
+        <v>95399</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1968</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435851</v>
+        <v>435973</v>
       </c>
       <c r="R50" t="n">
-        <v>6737817</v>
+        <v>6737875</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374882</v>
+        <v>121374879</v>
       </c>
       <c r="B51" t="n">
-        <v>90734</v>
+        <v>91653</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5815,25 +5815,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>4769</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435870</v>
+        <v>435838</v>
       </c>
       <c r="R51" t="n">
-        <v>6737805</v>
+        <v>6737809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347836</v>
+        <v>121347381</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>78643</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435602</v>
+        <v>435997</v>
       </c>
       <c r="R4" t="n">
-        <v>6737684</v>
+        <v>6737899</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121348221</v>
+        <v>121347743</v>
       </c>
       <c r="B5" t="n">
         <v>98105</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435979</v>
+        <v>435764</v>
       </c>
       <c r="R5" t="n">
-        <v>6737851</v>
+        <v>6737744</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347401</v>
+        <v>121348177</v>
       </c>
       <c r="B6" t="n">
-        <v>95399</v>
+        <v>90685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435964</v>
+        <v>435961</v>
       </c>
       <c r="R6" t="n">
-        <v>6737892</v>
+        <v>6737833</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347412</v>
+        <v>121347836</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,47 +1254,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435964</v>
+        <v>435602</v>
       </c>
       <c r="R7" t="n">
-        <v>6737892</v>
+        <v>6737684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347216</v>
+        <v>121347838</v>
       </c>
       <c r="B8" t="n">
-        <v>79227</v>
+        <v>91160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,38 +1356,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436129</v>
+        <v>435602</v>
       </c>
       <c r="R8" t="n">
-        <v>6737975</v>
+        <v>6737684</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346680</v>
+        <v>121347315</v>
       </c>
       <c r="B9" t="n">
-        <v>78345</v>
+        <v>80566</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436183</v>
+        <v>436015</v>
       </c>
       <c r="R9" t="n">
-        <v>6738020</v>
+        <v>6737908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347949</v>
+        <v>121348251</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,47 +1560,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435576</v>
+        <v>436011</v>
       </c>
       <c r="R10" t="n">
-        <v>6737633</v>
+        <v>6737862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121348117</v>
+        <v>121347759</v>
       </c>
       <c r="B11" t="n">
-        <v>100371</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,25 +1662,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435853</v>
+        <v>435691</v>
       </c>
       <c r="R11" t="n">
-        <v>6737770</v>
+        <v>6737739</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347087</v>
+        <v>121347275</v>
       </c>
       <c r="B12" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,35 +1764,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,10 +1801,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436159</v>
+        <v>436019</v>
       </c>
       <c r="R12" t="n">
-        <v>6737985</v>
+        <v>6737925</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1881,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121348251</v>
+        <v>121347826</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1893,38 +1875,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436011</v>
+        <v>435632</v>
       </c>
       <c r="R13" t="n">
-        <v>6737862</v>
+        <v>6737702</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347180</v>
+        <v>121347953</v>
       </c>
       <c r="B14" t="n">
-        <v>79227</v>
+        <v>100371</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,38 +1986,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436132</v>
+        <v>435579</v>
       </c>
       <c r="R14" t="n">
-        <v>6737977</v>
+        <v>6737637</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121348177</v>
+        <v>121348221</v>
       </c>
       <c r="B15" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,38 +2088,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435961</v>
+        <v>435979</v>
       </c>
       <c r="R15" t="n">
-        <v>6737833</v>
+        <v>6737851</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347759</v>
+        <v>121346697</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>74654</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,38 +2199,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>435691</v>
+        <v>436180</v>
       </c>
       <c r="R16" t="n">
-        <v>6737739</v>
+        <v>6737996</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347858</v>
+        <v>121347180</v>
       </c>
       <c r="B18" t="n">
-        <v>100371</v>
+        <v>79227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,38 +2403,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>435596</v>
+        <v>436132</v>
       </c>
       <c r="R18" t="n">
-        <v>6737662</v>
+        <v>6737977</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347925</v>
+        <v>121347087</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,47 +2505,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435579</v>
+        <v>436159</v>
       </c>
       <c r="R19" t="n">
-        <v>6737662</v>
+        <v>6737985</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,10 +2604,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347953</v>
+        <v>121347142</v>
       </c>
       <c r="B20" t="n">
-        <v>100371</v>
+        <v>78643</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,38 +2616,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435579</v>
+        <v>436148</v>
       </c>
       <c r="R20" t="n">
-        <v>6737637</v>
+        <v>6737987</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347170</v>
+        <v>121347925</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,38 +2718,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436138</v>
+        <v>435579</v>
       </c>
       <c r="R21" t="n">
-        <v>6737980</v>
+        <v>6737662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2808,7 +2817,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347826</v>
+        <v>121347503</v>
       </c>
       <c r="B22" t="n">
         <v>98105</v>
@@ -2857,10 +2866,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435632</v>
+        <v>435899</v>
       </c>
       <c r="R22" t="n">
-        <v>6737702</v>
+        <v>6737841</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,10 +2928,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346735</v>
+        <v>121348117</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>100371</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2931,38 +2940,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436168</v>
+        <v>435853</v>
       </c>
       <c r="R23" t="n">
-        <v>6737999</v>
+        <v>6737770</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3021,7 +3030,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346697</v>
+        <v>121346658</v>
       </c>
       <c r="B24" t="n">
         <v>74654</v>
@@ -3061,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436180</v>
+        <v>436188</v>
       </c>
       <c r="R24" t="n">
-        <v>6737996</v>
+        <v>6738012</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,10 +3132,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347321</v>
+        <v>121346881</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>78643</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,21 +3148,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436013</v>
+        <v>436163</v>
       </c>
       <c r="R25" t="n">
-        <v>6737929</v>
+        <v>6737990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3225,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347743</v>
+        <v>121347321</v>
       </c>
       <c r="B26" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,47 +3246,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435764</v>
+        <v>436013</v>
       </c>
       <c r="R26" t="n">
-        <v>6737744</v>
+        <v>6737929</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346569</v>
+        <v>121347401</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>95399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,38 +3348,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436212</v>
+        <v>435964</v>
       </c>
       <c r="R27" t="n">
-        <v>6737992</v>
+        <v>6737892</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347275</v>
+        <v>121347850</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>94507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,47 +3450,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436019</v>
+        <v>435603</v>
       </c>
       <c r="R28" t="n">
-        <v>6737925</v>
+        <v>6737665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3549,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347503</v>
+        <v>121346680</v>
       </c>
       <c r="B29" t="n">
-        <v>98105</v>
+        <v>78345</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3561,47 +3552,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435899</v>
+        <v>436183</v>
       </c>
       <c r="R29" t="n">
-        <v>6737841</v>
+        <v>6738020</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3660,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121346658</v>
+        <v>121347170</v>
       </c>
       <c r="B30" t="n">
-        <v>74654</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3672,25 +3654,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3700,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436188</v>
+        <v>436138</v>
       </c>
       <c r="R30" t="n">
-        <v>6738012</v>
+        <v>6737980</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3762,10 +3744,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346682</v>
+        <v>121347858</v>
       </c>
       <c r="B31" t="n">
-        <v>78346</v>
+        <v>100371</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,38 +3756,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436183</v>
+        <v>435596</v>
       </c>
       <c r="R31" t="n">
-        <v>6738020</v>
+        <v>6737662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3864,10 +3846,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347381</v>
+        <v>121347949</v>
       </c>
       <c r="B32" t="n">
-        <v>78643</v>
+        <v>98105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,38 +3858,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435997</v>
+        <v>435576</v>
       </c>
       <c r="R32" t="n">
-        <v>6737899</v>
+        <v>6737633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121346881</v>
+        <v>121346569</v>
       </c>
       <c r="B33" t="n">
-        <v>78643</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3982,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4006,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436163</v>
+        <v>436212</v>
       </c>
       <c r="R33" t="n">
-        <v>6737990</v>
+        <v>6737992</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4068,10 +4059,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347142</v>
+        <v>121347412</v>
       </c>
       <c r="B34" t="n">
-        <v>78643</v>
+        <v>98105</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,38 +4071,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436148</v>
+        <v>435964</v>
       </c>
       <c r="R34" t="n">
-        <v>6737987</v>
+        <v>6737892</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347315</v>
+        <v>121347961</v>
       </c>
       <c r="B35" t="n">
-        <v>80566</v>
+        <v>100371</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4182,25 +4182,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436015</v>
+        <v>435592</v>
       </c>
       <c r="R35" t="n">
-        <v>6737908</v>
+        <v>6737627</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347961</v>
+        <v>121347216</v>
       </c>
       <c r="B37" t="n">
-        <v>100371</v>
+        <v>79227</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4386,38 +4386,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>435592</v>
+        <v>436129</v>
       </c>
       <c r="R37" t="n">
-        <v>6737627</v>
+        <v>6737975</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347838</v>
+        <v>121346617</v>
       </c>
       <c r="B38" t="n">
-        <v>91160</v>
+        <v>79227</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4488,38 +4488,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435602</v>
+        <v>436197</v>
       </c>
       <c r="R38" t="n">
-        <v>6737684</v>
+        <v>6737992</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346617</v>
+        <v>121346735</v>
       </c>
       <c r="B39" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436197</v>
+        <v>436168</v>
       </c>
       <c r="R39" t="n">
-        <v>6737992</v>
+        <v>6737999</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121347850</v>
+        <v>121346682</v>
       </c>
       <c r="B40" t="n">
-        <v>94507</v>
+        <v>78346</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4692,38 +4692,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2809</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>435603</v>
+        <v>436183</v>
       </c>
       <c r="R40" t="n">
-        <v>6737665</v>
+        <v>6738020</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374881</v>
+        <v>121374879</v>
       </c>
       <c r="B41" t="n">
-        <v>92027</v>
+        <v>91653</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4794,25 +4794,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1968</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435851</v>
+        <v>435838</v>
       </c>
       <c r="R41" t="n">
-        <v>6737817</v>
+        <v>6737809</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374899</v>
+        <v>121374891</v>
       </c>
       <c r="B42" t="n">
-        <v>92004</v>
+        <v>100280</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2058</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436217</v>
+        <v>435907</v>
       </c>
       <c r="R42" t="n">
-        <v>6737988</v>
+        <v>6737812</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4968,6 +4968,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4986,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374891</v>
+        <v>121374883</v>
       </c>
       <c r="B43" t="n">
-        <v>100280</v>
+        <v>91653</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5002,21 +5003,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435907</v>
+        <v>435879</v>
       </c>
       <c r="R43" t="n">
-        <v>6737812</v>
+        <v>6737803</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5070,7 +5071,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5089,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374889</v>
+        <v>121374885</v>
       </c>
       <c r="B44" t="n">
-        <v>92008</v>
+        <v>98441</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5105,21 +5105,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>219880</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435889</v>
+        <v>435878</v>
       </c>
       <c r="R44" t="n">
-        <v>6737819</v>
+        <v>6737810</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374886</v>
+        <v>121374899</v>
       </c>
       <c r="B45" t="n">
-        <v>91998</v>
+        <v>92004</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,25 +5203,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>788</v>
+        <v>2058</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435868</v>
+        <v>436217</v>
       </c>
       <c r="R45" t="n">
-        <v>6737835</v>
+        <v>6737988</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374885</v>
+        <v>121374881</v>
       </c>
       <c r="B46" t="n">
-        <v>98441</v>
+        <v>92027</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219880</v>
+        <v>1968</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435878</v>
+        <v>435851</v>
       </c>
       <c r="R46" t="n">
-        <v>6737810</v>
+        <v>6737817</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374888</v>
+        <v>121374892</v>
       </c>
       <c r="B47" t="n">
-        <v>91403</v>
+        <v>95399</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5411,21 +5411,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3298</v>
+        <v>2869</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435889</v>
+        <v>435973</v>
       </c>
       <c r="R47" t="n">
-        <v>6737827</v>
+        <v>6737875</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374883</v>
+        <v>121374888</v>
       </c>
       <c r="B49" t="n">
-        <v>91653</v>
+        <v>91403</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435879</v>
+        <v>435889</v>
       </c>
       <c r="R49" t="n">
-        <v>6737803</v>
+        <v>6737827</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374892</v>
+        <v>121374889</v>
       </c>
       <c r="B50" t="n">
-        <v>95399</v>
+        <v>92008</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5717,21 +5717,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435973</v>
+        <v>435889</v>
       </c>
       <c r="R50" t="n">
-        <v>6737875</v>
+        <v>6737819</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374879</v>
+        <v>121374886</v>
       </c>
       <c r="B51" t="n">
-        <v>91653</v>
+        <v>91998</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5815,25 +5815,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435838</v>
+        <v>435868</v>
       </c>
       <c r="R51" t="n">
-        <v>6737809</v>
+        <v>6737835</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347381</v>
+        <v>121347412</v>
       </c>
       <c r="B4" t="n">
-        <v>78643</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,38 +939,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435997</v>
+        <v>435964</v>
       </c>
       <c r="R4" t="n">
-        <v>6737899</v>
+        <v>6737892</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347743</v>
+        <v>121346569</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,47 +1050,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>435764</v>
+        <v>436212</v>
       </c>
       <c r="R5" t="n">
-        <v>6737744</v>
+        <v>6737992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121348177</v>
+        <v>121347925</v>
       </c>
       <c r="B6" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,38 +1152,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435961</v>
+        <v>435579</v>
       </c>
       <c r="R6" t="n">
-        <v>6737833</v>
+        <v>6737662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347836</v>
+        <v>121347315</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>80566</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>435602</v>
+        <v>436015</v>
       </c>
       <c r="R7" t="n">
-        <v>6737684</v>
+        <v>6737908</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347838</v>
+        <v>121347180</v>
       </c>
       <c r="B8" t="n">
-        <v>91160</v>
+        <v>79227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,38 +1365,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>435602</v>
+        <v>436132</v>
       </c>
       <c r="R8" t="n">
-        <v>6737684</v>
+        <v>6737977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347315</v>
+        <v>121347949</v>
       </c>
       <c r="B9" t="n">
-        <v>80566</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,38 +1467,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436015</v>
+        <v>435576</v>
       </c>
       <c r="R9" t="n">
-        <v>6737908</v>
+        <v>6737633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121348251</v>
+        <v>121347850</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>94507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1578,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436011</v>
+        <v>435603</v>
       </c>
       <c r="R10" t="n">
-        <v>6737862</v>
+        <v>6737665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347759</v>
+        <v>121347216</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,34 +1684,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>435691</v>
+        <v>436129</v>
       </c>
       <c r="R11" t="n">
-        <v>6737739</v>
+        <v>6737975</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347275</v>
+        <v>121347170</v>
       </c>
       <c r="B12" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,47 +1782,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436019</v>
+        <v>436138</v>
       </c>
       <c r="R12" t="n">
-        <v>6737925</v>
+        <v>6737980</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,7 +1872,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347826</v>
+        <v>121348221</v>
       </c>
       <c r="B13" t="n">
         <v>98105</v>
@@ -1898,7 +1907,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1912,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435632</v>
+        <v>435979</v>
       </c>
       <c r="R13" t="n">
-        <v>6737702</v>
+        <v>6737851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347953</v>
+        <v>121347401</v>
       </c>
       <c r="B14" t="n">
-        <v>100371</v>
+        <v>95399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,21 +1999,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435579</v>
+        <v>435964</v>
       </c>
       <c r="R14" t="n">
-        <v>6737637</v>
+        <v>6737892</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121348221</v>
+        <v>121346658</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>74654</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,47 +2097,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435979</v>
+        <v>436188</v>
       </c>
       <c r="R15" t="n">
-        <v>6737851</v>
+        <v>6738012</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346697</v>
+        <v>121346881</v>
       </c>
       <c r="B16" t="n">
-        <v>74654</v>
+        <v>78643</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,25 +2199,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436180</v>
+        <v>436163</v>
       </c>
       <c r="R16" t="n">
-        <v>6737996</v>
+        <v>6737990</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121348302</v>
+        <v>121347381</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,34 +2305,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436091</v>
+        <v>435997</v>
       </c>
       <c r="R17" t="n">
-        <v>6737907</v>
+        <v>6737899</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347180</v>
+        <v>121347275</v>
       </c>
       <c r="B18" t="n">
-        <v>79227</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,38 +2403,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436132</v>
+        <v>436019</v>
       </c>
       <c r="R18" t="n">
-        <v>6737977</v>
+        <v>6737925</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347087</v>
+        <v>121347826</v>
       </c>
       <c r="B19" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,47 +2514,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436159</v>
+        <v>435632</v>
       </c>
       <c r="R19" t="n">
-        <v>6737985</v>
+        <v>6737702</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347142</v>
+        <v>121347503</v>
       </c>
       <c r="B20" t="n">
-        <v>78643</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2616,38 +2625,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436148</v>
+        <v>435899</v>
       </c>
       <c r="R20" t="n">
-        <v>6737987</v>
+        <v>6737841</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2706,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347925</v>
+        <v>121348117</v>
       </c>
       <c r="B21" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2718,47 +2736,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435579</v>
+        <v>435853</v>
       </c>
       <c r="R21" t="n">
-        <v>6737662</v>
+        <v>6737770</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,10 +2826,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347503</v>
+        <v>121346697</v>
       </c>
       <c r="B22" t="n">
-        <v>98105</v>
+        <v>74654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2829,47 +2838,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>435899</v>
+        <v>436180</v>
       </c>
       <c r="R22" t="n">
-        <v>6737841</v>
+        <v>6737996</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121348117</v>
+        <v>121347759</v>
       </c>
       <c r="B23" t="n">
-        <v>100371</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435853</v>
+        <v>435691</v>
       </c>
       <c r="R23" t="n">
-        <v>6737770</v>
+        <v>6737739</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346658</v>
+        <v>121346617</v>
       </c>
       <c r="B24" t="n">
-        <v>74654</v>
+        <v>79227</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436188</v>
+        <v>436197</v>
       </c>
       <c r="R24" t="n">
-        <v>6738012</v>
+        <v>6737992</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346881</v>
+        <v>121347836</v>
       </c>
       <c r="B25" t="n">
-        <v>78643</v>
+        <v>90720</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3148,34 +3148,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436163</v>
+        <v>435602</v>
       </c>
       <c r="R25" t="n">
-        <v>6737990</v>
+        <v>6737684</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347321</v>
+        <v>121347838</v>
       </c>
       <c r="B26" t="n">
-        <v>90720</v>
+        <v>91160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3246,38 +3246,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436013</v>
+        <v>435602</v>
       </c>
       <c r="R26" t="n">
-        <v>6737929</v>
+        <v>6737684</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347401</v>
+        <v>121347743</v>
       </c>
       <c r="B27" t="n">
-        <v>95399</v>
+        <v>98105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,38 +3348,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435964</v>
+        <v>435764</v>
       </c>
       <c r="R27" t="n">
-        <v>6737892</v>
+        <v>6737744</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3438,10 +3447,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347850</v>
+        <v>121346787</v>
       </c>
       <c r="B28" t="n">
-        <v>94507</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,38 +3459,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>435603</v>
+        <v>436175</v>
       </c>
       <c r="R28" t="n">
-        <v>6737665</v>
+        <v>6737983</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346680</v>
+        <v>121347961</v>
       </c>
       <c r="B29" t="n">
-        <v>78345</v>
+        <v>100371</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3552,38 +3561,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436183</v>
+        <v>435592</v>
       </c>
       <c r="R29" t="n">
-        <v>6738020</v>
+        <v>6737627</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3642,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347170</v>
+        <v>121347858</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>100371</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3654,38 +3663,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436138</v>
+        <v>435596</v>
       </c>
       <c r="R30" t="n">
-        <v>6737980</v>
+        <v>6737662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3744,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121347858</v>
+        <v>121348251</v>
       </c>
       <c r="B31" t="n">
-        <v>100371</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3756,25 +3765,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3784,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435596</v>
+        <v>436011</v>
       </c>
       <c r="R31" t="n">
-        <v>6737662</v>
+        <v>6737862</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3846,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347949</v>
+        <v>121347321</v>
       </c>
       <c r="B32" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,47 +3867,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>435576</v>
+        <v>436013</v>
       </c>
       <c r="R32" t="n">
-        <v>6737633</v>
+        <v>6737929</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121346569</v>
+        <v>121348302</v>
       </c>
       <c r="B33" t="n">
         <v>78609</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436212</v>
+        <v>436091</v>
       </c>
       <c r="R33" t="n">
-        <v>6737992</v>
+        <v>6737907</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4059,10 +4059,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347412</v>
+        <v>121347087</v>
       </c>
       <c r="B34" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4071,47 +4071,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>435964</v>
+        <v>436159</v>
       </c>
       <c r="R34" t="n">
-        <v>6737892</v>
+        <v>6737985</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347961</v>
+        <v>121347953</v>
       </c>
       <c r="B35" t="n">
         <v>100371</v>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435592</v>
+        <v>435579</v>
       </c>
       <c r="R35" t="n">
-        <v>6737627</v>
+        <v>6737637</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121346787</v>
+        <v>121347142</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>78643</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4288,21 +4288,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436175</v>
+        <v>436148</v>
       </c>
       <c r="R36" t="n">
-        <v>6737983</v>
+        <v>6737987</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347216</v>
+        <v>121346735</v>
       </c>
       <c r="B37" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436129</v>
+        <v>436168</v>
       </c>
       <c r="R37" t="n">
-        <v>6737975</v>
+        <v>6737999</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121346617</v>
+        <v>121348177</v>
       </c>
       <c r="B38" t="n">
-        <v>79227</v>
+        <v>90685</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4488,38 +4488,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436197</v>
+        <v>435961</v>
       </c>
       <c r="R38" t="n">
-        <v>6737992</v>
+        <v>6737833</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346735</v>
+        <v>121346682</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436168</v>
+        <v>436183</v>
       </c>
       <c r="R39" t="n">
-        <v>6737999</v>
+        <v>6738020</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121346682</v>
+        <v>121346680</v>
       </c>
       <c r="B40" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4696,21 +4696,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374879</v>
+        <v>121374888</v>
       </c>
       <c r="B41" t="n">
-        <v>91653</v>
+        <v>91403</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435838</v>
+        <v>435889</v>
       </c>
       <c r="R41" t="n">
-        <v>6737809</v>
+        <v>6737827</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374891</v>
+        <v>121374881</v>
       </c>
       <c r="B42" t="n">
-        <v>100280</v>
+        <v>92027</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>1968</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435907</v>
+        <v>435851</v>
       </c>
       <c r="R42" t="n">
-        <v>6737812</v>
+        <v>6737817</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4968,7 +4968,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4987,10 +4986,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374883</v>
+        <v>121374885</v>
       </c>
       <c r="B43" t="n">
-        <v>91653</v>
+        <v>98441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5003,21 +5002,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>219880</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5027,10 +5026,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435879</v>
+        <v>435878</v>
       </c>
       <c r="R43" t="n">
-        <v>6737803</v>
+        <v>6737810</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,10 +5088,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374885</v>
+        <v>121374891</v>
       </c>
       <c r="B44" t="n">
-        <v>98441</v>
+        <v>100280</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5105,21 +5104,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219880</v>
+        <v>222771</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5129,10 +5128,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435878</v>
+        <v>435907</v>
       </c>
       <c r="R44" t="n">
-        <v>6737810</v>
+        <v>6737812</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5173,6 +5172,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374899</v>
+        <v>121374879</v>
       </c>
       <c r="B45" t="n">
-        <v>92004</v>
+        <v>91653</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,25 +5203,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2058</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436217</v>
+        <v>435838</v>
       </c>
       <c r="R45" t="n">
-        <v>6737988</v>
+        <v>6737809</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374881</v>
+        <v>121374889</v>
       </c>
       <c r="B46" t="n">
-        <v>92027</v>
+        <v>92008</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435851</v>
+        <v>435889</v>
       </c>
       <c r="R46" t="n">
-        <v>6737817</v>
+        <v>6737819</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374892</v>
+        <v>121374899</v>
       </c>
       <c r="B47" t="n">
-        <v>95399</v>
+        <v>92004</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,25 +5407,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2869</v>
+        <v>2058</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>435973</v>
+        <v>436217</v>
       </c>
       <c r="R47" t="n">
-        <v>6737875</v>
+        <v>6737988</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374882</v>
+        <v>121374883</v>
       </c>
       <c r="B48" t="n">
-        <v>90734</v>
+        <v>91653</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5509,25 +5509,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>4769</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435870</v>
+        <v>435879</v>
       </c>
       <c r="R48" t="n">
-        <v>6737805</v>
+        <v>6737803</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374888</v>
+        <v>121374886</v>
       </c>
       <c r="B49" t="n">
-        <v>91403</v>
+        <v>91998</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,25 +5611,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>788</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435889</v>
+        <v>435868</v>
       </c>
       <c r="R49" t="n">
-        <v>6737827</v>
+        <v>6737835</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374889</v>
+        <v>121374892</v>
       </c>
       <c r="B50" t="n">
-        <v>92008</v>
+        <v>95399</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5717,21 +5717,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435889</v>
+        <v>435973</v>
       </c>
       <c r="R50" t="n">
-        <v>6737819</v>
+        <v>6737875</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374886</v>
+        <v>121374882</v>
       </c>
       <c r="B51" t="n">
-        <v>91998</v>
+        <v>90734</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>788</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435868</v>
+        <v>435870</v>
       </c>
       <c r="R51" t="n">
-        <v>6737835</v>
+        <v>6737805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121348221</v>
+        <v>121347401</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>95399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,47 +1884,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435979</v>
+        <v>435964</v>
       </c>
       <c r="R13" t="n">
-        <v>6737851</v>
+        <v>6737892</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347401</v>
+        <v>121346658</v>
       </c>
       <c r="B14" t="n">
-        <v>95399</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,34 +1990,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>435964</v>
+        <v>436188</v>
       </c>
       <c r="R14" t="n">
-        <v>6737892</v>
+        <v>6738012</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2085,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346658</v>
+        <v>121348221</v>
       </c>
       <c r="B15" t="n">
-        <v>74654</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,38 +2088,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436188</v>
+        <v>435979</v>
       </c>
       <c r="R15" t="n">
-        <v>6738012</v>
+        <v>6737851</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347743</v>
+        <v>121347961</v>
       </c>
       <c r="B27" t="n">
-        <v>98105</v>
+        <v>100371</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,47 +3348,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435764</v>
+        <v>435592</v>
       </c>
       <c r="R27" t="n">
-        <v>6737744</v>
+        <v>6737627</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347961</v>
+        <v>121347743</v>
       </c>
       <c r="B29" t="n">
-        <v>100371</v>
+        <v>98105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3561,38 +3552,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435592</v>
+        <v>435764</v>
       </c>
       <c r="R29" t="n">
-        <v>6737627</v>
+        <v>6737744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121348251</v>
+        <v>121347321</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,34 +3769,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436011</v>
+        <v>436013</v>
       </c>
       <c r="R31" t="n">
-        <v>6737862</v>
+        <v>6737929</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347321</v>
+        <v>121348251</v>
       </c>
       <c r="B32" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,34 +3871,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436013</v>
+        <v>436011</v>
       </c>
       <c r="R32" t="n">
-        <v>6737929</v>
+        <v>6737862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -1668,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347216</v>
+        <v>121347170</v>
       </c>
       <c r="B11" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1684,21 +1684,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436129</v>
+        <v>436138</v>
       </c>
       <c r="R11" t="n">
-        <v>6737975</v>
+        <v>6737980</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347170</v>
+        <v>121347216</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,21 +1786,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436138</v>
+        <v>436129</v>
       </c>
       <c r="R12" t="n">
-        <v>6737980</v>
+        <v>6737975</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121347321</v>
+        <v>121348251</v>
       </c>
       <c r="B31" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3769,34 +3769,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436013</v>
+        <v>436011</v>
       </c>
       <c r="R31" t="n">
-        <v>6737929</v>
+        <v>6737862</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121348251</v>
+        <v>121347321</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3871,34 +3871,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436011</v>
+        <v>436013</v>
       </c>
       <c r="R32" t="n">
-        <v>6737862</v>
+        <v>6737929</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346735</v>
+        <v>121346682</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436168</v>
+        <v>436183</v>
       </c>
       <c r="R37" t="n">
-        <v>6737999</v>
+        <v>6738020</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121348177</v>
+        <v>121346735</v>
       </c>
       <c r="B38" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4488,38 +4488,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>435961</v>
+        <v>436168</v>
       </c>
       <c r="R38" t="n">
-        <v>6737833</v>
+        <v>6737999</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346682</v>
+        <v>121348177</v>
       </c>
       <c r="B39" t="n">
-        <v>78346</v>
+        <v>90685</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4590,38 +4590,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436183</v>
+        <v>435961</v>
       </c>
       <c r="R39" t="n">
-        <v>6738020</v>
+        <v>6737833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374892</v>
+        <v>121374882</v>
       </c>
       <c r="B50" t="n">
-        <v>95399</v>
+        <v>90734</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435973</v>
+        <v>435870</v>
       </c>
       <c r="R50" t="n">
-        <v>6737875</v>
+        <v>6737805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374882</v>
+        <v>121374892</v>
       </c>
       <c r="B51" t="n">
-        <v>90734</v>
+        <v>95399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5815,25 +5815,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435870</v>
+        <v>435973</v>
       </c>
       <c r="R51" t="n">
-        <v>6737805</v>
+        <v>6737875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347412</v>
+        <v>121347759</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,47 +939,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>435964</v>
+        <v>435691</v>
       </c>
       <c r="R4" t="n">
-        <v>6737892</v>
+        <v>6737739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1038,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346569</v>
+        <v>121346680</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78352</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436212</v>
+        <v>436183</v>
       </c>
       <c r="R5" t="n">
-        <v>6737992</v>
+        <v>6738020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347925</v>
+        <v>121347087</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,47 +1143,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435579</v>
+        <v>436159</v>
       </c>
       <c r="R6" t="n">
-        <v>6737662</v>
+        <v>6737985</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347315</v>
+        <v>121347180</v>
       </c>
       <c r="B7" t="n">
-        <v>80566</v>
+        <v>79234</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,34 +1258,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436015</v>
+        <v>436132</v>
       </c>
       <c r="R7" t="n">
-        <v>6737908</v>
+        <v>6737977</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347180</v>
+        <v>121347412</v>
       </c>
       <c r="B8" t="n">
-        <v>79227</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,38 +1356,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436132</v>
+        <v>435964</v>
       </c>
       <c r="R8" t="n">
-        <v>6737977</v>
+        <v>6737892</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347949</v>
+        <v>121347216</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>79234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,47 +1467,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>435576</v>
+        <v>436129</v>
       </c>
       <c r="R9" t="n">
-        <v>6737633</v>
+        <v>6737975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347850</v>
+        <v>121347170</v>
       </c>
       <c r="B10" t="n">
-        <v>94507</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,38 +1569,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>435603</v>
+        <v>436138</v>
       </c>
       <c r="R10" t="n">
-        <v>6737665</v>
+        <v>6737980</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,10 +1659,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347170</v>
+        <v>121347953</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>100379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,38 +1671,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436138</v>
+        <v>435579</v>
       </c>
       <c r="R11" t="n">
-        <v>6737980</v>
+        <v>6737637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347216</v>
+        <v>121347743</v>
       </c>
       <c r="B12" t="n">
-        <v>79227</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,38 +1773,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436129</v>
+        <v>435764</v>
       </c>
       <c r="R12" t="n">
-        <v>6737975</v>
+        <v>6737744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347401</v>
+        <v>121347949</v>
       </c>
       <c r="B13" t="n">
-        <v>95399</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,38 +1884,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>435964</v>
+        <v>435576</v>
       </c>
       <c r="R13" t="n">
-        <v>6737892</v>
+        <v>6737633</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346658</v>
+        <v>121346569</v>
       </c>
       <c r="B14" t="n">
-        <v>74654</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436188</v>
+        <v>436212</v>
       </c>
       <c r="R14" t="n">
-        <v>6738012</v>
+        <v>6737992</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121348221</v>
+        <v>121348251</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2088,47 +2097,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>435979</v>
+        <v>436011</v>
       </c>
       <c r="R15" t="n">
-        <v>6737851</v>
+        <v>6737862</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346881</v>
+        <v>121348221</v>
       </c>
       <c r="B16" t="n">
-        <v>78643</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,38 +2199,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436163</v>
+        <v>435979</v>
       </c>
       <c r="R16" t="n">
-        <v>6737990</v>
+        <v>6737851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347381</v>
+        <v>121346682</v>
       </c>
       <c r="B17" t="n">
-        <v>78643</v>
+        <v>78353</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,34 +2314,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>435997</v>
+        <v>436183</v>
       </c>
       <c r="R17" t="n">
-        <v>6737899</v>
+        <v>6738020</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347275</v>
+        <v>121347381</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>78650</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,47 +2412,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436019</v>
+        <v>435997</v>
       </c>
       <c r="R18" t="n">
-        <v>6737925</v>
+        <v>6737899</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347826</v>
+        <v>121347275</v>
       </c>
       <c r="B19" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2547,14 +2547,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>435632</v>
+        <v>436019</v>
       </c>
       <c r="R19" t="n">
-        <v>6737702</v>
+        <v>6737925</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347503</v>
+        <v>121348117</v>
       </c>
       <c r="B20" t="n">
-        <v>98105</v>
+        <v>100379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2625,47 +2625,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>435899</v>
+        <v>435853</v>
       </c>
       <c r="R20" t="n">
-        <v>6737841</v>
+        <v>6737770</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,10 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121348117</v>
+        <v>121347858</v>
       </c>
       <c r="B21" t="n">
-        <v>100371</v>
+        <v>100379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2764,10 +2755,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>435853</v>
+        <v>435596</v>
       </c>
       <c r="R21" t="n">
-        <v>6737770</v>
+        <v>6737662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2826,10 +2817,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121346697</v>
+        <v>121348177</v>
       </c>
       <c r="B22" t="n">
-        <v>74654</v>
+        <v>90693</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2842,34 +2833,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436180</v>
+        <v>435961</v>
       </c>
       <c r="R22" t="n">
-        <v>6737996</v>
+        <v>6737833</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2928,10 +2919,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347759</v>
+        <v>121346787</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,14 +2955,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>435691</v>
+        <v>436175</v>
       </c>
       <c r="R23" t="n">
-        <v>6737739</v>
+        <v>6737983</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346617</v>
+        <v>121347826</v>
       </c>
       <c r="B24" t="n">
-        <v>79227</v>
+        <v>98113</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,38 +3033,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436197</v>
+        <v>435632</v>
       </c>
       <c r="R24" t="n">
-        <v>6737992</v>
+        <v>6737702</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347836</v>
+        <v>121346617</v>
       </c>
       <c r="B25" t="n">
-        <v>90720</v>
+        <v>79234</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3148,34 +3148,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>435602</v>
+        <v>436197</v>
       </c>
       <c r="R25" t="n">
-        <v>6737684</v>
+        <v>6737992</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347838</v>
+        <v>121346697</v>
       </c>
       <c r="B26" t="n">
-        <v>91160</v>
+        <v>74661</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3246,38 +3246,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>435602</v>
+        <v>436180</v>
       </c>
       <c r="R26" t="n">
-        <v>6737684</v>
+        <v>6737996</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347961</v>
+        <v>121347925</v>
       </c>
       <c r="B27" t="n">
-        <v>100371</v>
+        <v>98113</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,38 +3348,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>435592</v>
+        <v>435579</v>
       </c>
       <c r="R27" t="n">
-        <v>6737627</v>
+        <v>6737662</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3438,10 +3447,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346787</v>
+        <v>121346881</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>78650</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3454,21 +3463,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3478,10 +3487,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436175</v>
+        <v>436163</v>
       </c>
       <c r="R28" t="n">
-        <v>6737983</v>
+        <v>6737990</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347743</v>
+        <v>121347401</v>
       </c>
       <c r="B29" t="n">
-        <v>98105</v>
+        <v>95407</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3552,47 +3561,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435764</v>
+        <v>435964</v>
       </c>
       <c r="R29" t="n">
-        <v>6737744</v>
+        <v>6737892</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347858</v>
+        <v>121346735</v>
       </c>
       <c r="B30" t="n">
-        <v>100371</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3663,38 +3663,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435596</v>
+        <v>436168</v>
       </c>
       <c r="R30" t="n">
-        <v>6737662</v>
+        <v>6737999</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121348251</v>
+        <v>121347838</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>91168</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3765,25 +3765,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436011</v>
+        <v>435602</v>
       </c>
       <c r="R31" t="n">
-        <v>6737862</v>
+        <v>6737684</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121347321</v>
+        <v>121347836</v>
       </c>
       <c r="B32" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3891,14 +3891,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436013</v>
+        <v>435602</v>
       </c>
       <c r="R32" t="n">
-        <v>6737929</v>
+        <v>6737684</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
         <v>121348302</v>
       </c>
       <c r="B33" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121347087</v>
+        <v>121347321</v>
       </c>
       <c r="B34" t="n">
-        <v>57509</v>
+        <v>90728</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4075,43 +4075,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436159</v>
+        <v>436013</v>
       </c>
       <c r="R34" t="n">
-        <v>6737985</v>
+        <v>6737929</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4170,10 +4161,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121347953</v>
+        <v>121347503</v>
       </c>
       <c r="B35" t="n">
-        <v>100371</v>
+        <v>98113</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4182,38 +4173,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>435579</v>
+        <v>435899</v>
       </c>
       <c r="R35" t="n">
-        <v>6737637</v>
+        <v>6737841</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121347142</v>
+        <v>121347850</v>
       </c>
       <c r="B36" t="n">
-        <v>78643</v>
+        <v>94515</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4284,38 +4284,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>2809</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436148</v>
+        <v>435603</v>
       </c>
       <c r="R36" t="n">
-        <v>6737987</v>
+        <v>6737665</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121346682</v>
+        <v>121347142</v>
       </c>
       <c r="B37" t="n">
-        <v>78346</v>
+        <v>78650</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436183</v>
+        <v>436148</v>
       </c>
       <c r="R37" t="n">
-        <v>6738020</v>
+        <v>6737987</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121346735</v>
+        <v>121347315</v>
       </c>
       <c r="B38" t="n">
-        <v>78609</v>
+        <v>80573</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4492,34 +4492,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436168</v>
+        <v>436015</v>
       </c>
       <c r="R38" t="n">
-        <v>6737999</v>
+        <v>6737908</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121348177</v>
+        <v>121346658</v>
       </c>
       <c r="B39" t="n">
-        <v>90685</v>
+        <v>74661</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,34 +4594,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>435961</v>
+        <v>436188</v>
       </c>
       <c r="R39" t="n">
-        <v>6737833</v>
+        <v>6738012</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121346680</v>
+        <v>121347961</v>
       </c>
       <c r="B40" t="n">
-        <v>78345</v>
+        <v>100379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4692,38 +4692,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436183</v>
+        <v>435592</v>
       </c>
       <c r="R40" t="n">
-        <v>6738020</v>
+        <v>6737627</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121374888</v>
+        <v>121374879</v>
       </c>
       <c r="B41" t="n">
-        <v>91403</v>
+        <v>91661</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4798,21 +4798,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4822,10 +4822,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>435889</v>
+        <v>435838</v>
       </c>
       <c r="R41" t="n">
-        <v>6737827</v>
+        <v>6737809</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4884,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121374881</v>
+        <v>121374891</v>
       </c>
       <c r="B42" t="n">
-        <v>92027</v>
+        <v>100288</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1968</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>435851</v>
+        <v>435907</v>
       </c>
       <c r="R42" t="n">
-        <v>6737817</v>
+        <v>6737812</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4968,6 +4968,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4986,10 +4987,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121374885</v>
+        <v>121374892</v>
       </c>
       <c r="B43" t="n">
-        <v>98441</v>
+        <v>95407</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5002,21 +5003,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219880</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5026,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>435878</v>
+        <v>435973</v>
       </c>
       <c r="R43" t="n">
-        <v>6737810</v>
+        <v>6737875</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5088,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121374891</v>
+        <v>121374899</v>
       </c>
       <c r="B44" t="n">
-        <v>100280</v>
+        <v>92012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5100,25 +5101,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222771</v>
+        <v>2058</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5128,10 +5129,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>435907</v>
+        <v>436217</v>
       </c>
       <c r="R44" t="n">
-        <v>6737812</v>
+        <v>6737988</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5172,7 +5173,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121374879</v>
+        <v>121374886</v>
       </c>
       <c r="B45" t="n">
-        <v>91653</v>
+        <v>92006</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5203,25 +5203,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>788</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5231,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>435838</v>
+        <v>435868</v>
       </c>
       <c r="R45" t="n">
-        <v>6737809</v>
+        <v>6737835</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,10 +5293,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121374889</v>
+        <v>121374882</v>
       </c>
       <c r="B46" t="n">
-        <v>92008</v>
+        <v>90742</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5305,25 +5305,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4366</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>435889</v>
+        <v>435870</v>
       </c>
       <c r="R46" t="n">
-        <v>6737819</v>
+        <v>6737805</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121374899</v>
+        <v>121374881</v>
       </c>
       <c r="B47" t="n">
-        <v>92004</v>
+        <v>92035</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,25 +5407,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2058</v>
+        <v>1968</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5435,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436217</v>
+        <v>435851</v>
       </c>
       <c r="R47" t="n">
-        <v>6737988</v>
+        <v>6737817</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121374883</v>
+        <v>121374885</v>
       </c>
       <c r="B48" t="n">
-        <v>91653</v>
+        <v>98449</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5513,21 +5513,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4769</v>
+        <v>219880</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5537,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>435879</v>
+        <v>435878</v>
       </c>
       <c r="R48" t="n">
-        <v>6737803</v>
+        <v>6737810</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5599,10 +5599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121374886</v>
+        <v>121374883</v>
       </c>
       <c r="B49" t="n">
-        <v>91998</v>
+        <v>91661</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5611,25 +5611,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>788</v>
+        <v>4769</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>435868</v>
+        <v>435879</v>
       </c>
       <c r="R49" t="n">
-        <v>6737835</v>
+        <v>6737803</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121374882</v>
+        <v>121374888</v>
       </c>
       <c r="B50" t="n">
-        <v>90734</v>
+        <v>91411</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5713,25 +5713,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>435870</v>
+        <v>435889</v>
       </c>
       <c r="R50" t="n">
-        <v>6737805</v>
+        <v>6737827</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5803,10 +5803,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121374892</v>
+        <v>121374889</v>
       </c>
       <c r="B51" t="n">
-        <v>95399</v>
+        <v>92016</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5819,21 +5819,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5843,10 +5843,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>435973</v>
+        <v>435889</v>
       </c>
       <c r="R51" t="n">
-        <v>6737875</v>
+        <v>6737819</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -3549,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347401</v>
+        <v>121347838</v>
       </c>
       <c r="B29" t="n">
-        <v>95407</v>
+        <v>91168</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3561,25 +3561,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2869</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435964</v>
+        <v>435602</v>
       </c>
       <c r="R29" t="n">
-        <v>6737892</v>
+        <v>6737684</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121346735</v>
+        <v>121347401</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>95407</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3663,38 +3663,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436168</v>
+        <v>435964</v>
       </c>
       <c r="R30" t="n">
-        <v>6737999</v>
+        <v>6737892</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121347838</v>
+        <v>121346735</v>
       </c>
       <c r="B31" t="n">
-        <v>91168</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3765,38 +3765,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>435602</v>
+        <v>436168</v>
       </c>
       <c r="R31" t="n">
-        <v>6737684</v>
+        <v>6737999</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4272,10 +4272,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121347850</v>
+        <v>121347315</v>
       </c>
       <c r="B36" t="n">
-        <v>94515</v>
+        <v>80573</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4284,25 +4284,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2809</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>435603</v>
+        <v>436015</v>
       </c>
       <c r="R36" t="n">
-        <v>6737665</v>
+        <v>6737908</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4374,10 +4374,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121347142</v>
+        <v>121346658</v>
       </c>
       <c r="B37" t="n">
-        <v>78650</v>
+        <v>74661</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4386,25 +4386,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436148</v>
+        <v>436188</v>
       </c>
       <c r="R37" t="n">
-        <v>6737987</v>
+        <v>6738012</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4476,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121347315</v>
+        <v>121347142</v>
       </c>
       <c r="B38" t="n">
-        <v>80573</v>
+        <v>78650</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4492,34 +4492,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436015</v>
+        <v>436148</v>
       </c>
       <c r="R38" t="n">
-        <v>6737908</v>
+        <v>6737987</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4578,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121346658</v>
+        <v>121347850</v>
       </c>
       <c r="B39" t="n">
-        <v>74661</v>
+        <v>94515</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4594,34 +4594,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436188</v>
+        <v>435603</v>
       </c>
       <c r="R39" t="n">
-        <v>6738012</v>
+        <v>6737665</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 24716-2024 artfynd.xlsx
+++ b/artfynd/A 24716-2024 artfynd.xlsx
@@ -3549,10 +3549,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347838</v>
+        <v>121347401</v>
       </c>
       <c r="B29" t="n">
-        <v>91168</v>
+        <v>95407</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3561,25 +3561,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>2869</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>435602</v>
+        <v>435964</v>
       </c>
       <c r="R29" t="n">
-        <v>6737684</v>
+        <v>6737892</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121347401</v>
+        <v>121346735</v>
       </c>
       <c r="B30" t="n">
-        <v>95407</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3663,38 +3663,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öjsberget, Öjsberget, Dlr</t>
+          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>435964</v>
+        <v>436168</v>
       </c>
       <c r="R30" t="n">
-        <v>6737892</v>
+        <v>6737999</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121346735</v>
+        <v>121347838</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>91168</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3765,38 +3765,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storhammarskölen, Storhammarskölen, Dlr</t>
+          <t>Öjsberget, Öjsberget, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436168</v>
+        <v>435602</v>
       </c>
       <c r="R31" t="n">
-        <v>6737999</v>
+        <v>6737684</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
